--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBB1BB54-A179-469E-84C8-3058905F3F4D}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8FA143C-D6D0-4E6C-BE11-753F2764F16F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -4026,6 +4026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y787"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4110,7 +4111,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -4180,7 +4181,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -4250,7 +4251,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -4320,7 +4321,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -4390,7 +4391,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -4460,7 +4461,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -4530,7 +4531,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -4600,7 +4601,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -4670,7 +4671,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -4740,7 +4741,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -4810,7 +4811,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -4880,7 +4881,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -4950,7 +4951,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -5017,7 +5018,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -5086,7 +5087,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -5155,7 +5156,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -5224,7 +5225,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -5293,7 +5294,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -5354,7 +5355,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -5423,7 +5424,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -5492,7 +5493,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -5562,7 +5563,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -5632,7 +5633,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -5699,7 +5700,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -5763,7 +5764,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -5823,7 +5824,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -5886,7 +5887,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -5951,7 +5952,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -6013,7 +6014,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -6071,7 +6072,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -6129,7 +6130,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -6203,7 +6204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -6277,7 +6278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -6351,7 +6352,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -6499,7 +6500,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -6573,7 +6574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -6647,7 +6648,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>221</v>
       </c>
@@ -6711,7 +6712,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -6785,7 +6786,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -6859,7 +6860,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -6933,7 +6934,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -7007,7 +7008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -7081,7 +7082,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -7155,7 +7156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>222</v>
       </c>
@@ -7229,7 +7230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -7303,7 +7304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -7375,7 +7376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -7449,7 +7450,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -7523,7 +7524,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -7583,7 +7584,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -7657,7 +7658,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -7731,7 +7732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -7805,7 +7806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -7877,7 +7878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -7951,7 +7952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -8025,7 +8026,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -8097,7 +8098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -8171,7 +8172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -8245,7 +8246,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -8319,7 +8320,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -8393,7 +8394,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -8467,7 +8468,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -8541,7 +8542,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -8613,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -8687,7 +8688,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -8757,7 +8758,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -8831,7 +8832,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -8901,7 +8902,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -8971,7 +8972,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -9045,7 +9046,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -9117,7 +9118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -9191,7 +9192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -9265,7 +9266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -9339,7 +9340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -9413,7 +9414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -9487,7 +9488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -9561,7 +9562,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -9618,7 +9619,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -9674,7 +9675,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -9742,7 +9743,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -9804,7 +9805,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -9878,7 +9879,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -9952,7 +9953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -10026,7 +10027,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -10100,7 +10101,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -10174,7 +10175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -10248,7 +10249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -10310,7 +10311,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -10369,7 +10370,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -10427,7 +10428,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>326</v>
       </c>
@@ -10485,7 +10486,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -10545,7 +10546,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -10601,7 +10602,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -10659,7 +10660,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -10717,7 +10718,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -10773,7 +10774,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -10831,7 +10832,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -10889,7 +10890,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>367</v>
       </c>
@@ -10947,7 +10948,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -11005,7 +11006,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -11063,7 +11064,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -11119,7 +11120,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -11175,7 +11176,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -11231,7 +11232,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -11289,7 +11290,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -11347,7 +11348,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -11405,7 +11406,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -11461,7 +11462,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -11517,7 +11518,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -11573,7 +11574,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>491</v>
       </c>
@@ -11629,7 +11630,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -11685,7 +11686,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -11741,7 +11742,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -11797,7 +11798,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>495</v>
       </c>
@@ -11853,7 +11854,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -11909,7 +11910,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>497</v>
       </c>
@@ -11963,7 +11964,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>498</v>
       </c>
@@ -12019,7 +12020,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>499</v>
       </c>
@@ -12073,7 +12074,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>500</v>
       </c>
@@ -12129,7 +12130,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>501</v>
       </c>
@@ -12185,7 +12186,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>502</v>
       </c>
@@ -12241,7 +12242,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>503</v>
       </c>
@@ -12297,7 +12298,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>504</v>
       </c>
@@ -12353,7 +12354,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>505</v>
       </c>
@@ -12409,7 +12410,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>508</v>
       </c>
@@ -12465,7 +12466,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>522</v>
       </c>
@@ -12519,7 +12520,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>527</v>
       </c>
@@ -12571,7 +12572,7 @@
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>528</v>
       </c>
@@ -12626,7 +12627,7 @@
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>541</v>
       </c>
@@ -12680,7 +12681,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>542</v>
       </c>
@@ -12744,7 +12745,7 @@
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>542</v>
       </c>
@@ -12818,7 +12819,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>542</v>
       </c>
@@ -12892,7 +12893,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>542</v>
       </c>
@@ -12966,7 +12967,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>542</v>
       </c>
@@ -13040,7 +13041,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>546</v>
       </c>
@@ -13102,7 +13103,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -13173,7 +13174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -13244,7 +13245,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>546</v>
       </c>
@@ -13315,7 +13316,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>547</v>
       </c>
@@ -13369,7 +13370,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>552</v>
       </c>
@@ -13423,7 +13424,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>553</v>
       </c>
@@ -13477,7 +13478,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>556</v>
       </c>
@@ -13531,7 +13532,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>290</v>
       </c>
@@ -13604,7 +13605,7 @@
         <v>91.666666666666657</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -13678,7 +13679,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -13752,7 +13753,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -13826,7 +13827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -13900,7 +13901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -13974,7 +13975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -14048,7 +14049,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -14122,7 +14123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -14196,7 +14197,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>290</v>
       </c>
@@ -14270,7 +14271,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>77</v>
       </c>
@@ -14347,7 +14348,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>121</v>
       </c>
@@ -14424,7 +14425,7 @@
         <v>99.18</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>122</v>
       </c>
@@ -14501,7 +14502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>124</v>
       </c>
@@ -14578,7 +14579,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>125</v>
       </c>
@@ -14655,7 +14656,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>128</v>
       </c>
@@ -14732,7 +14733,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>172</v>
       </c>
@@ -14809,7 +14810,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>208</v>
       </c>
@@ -14886,7 +14887,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -14963,7 +14964,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -15040,7 +15041,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -15117,7 +15118,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -15194,7 +15195,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -15271,7 +15272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>208</v>
       </c>
@@ -15348,7 +15349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>214</v>
       </c>
@@ -15425,7 +15426,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -15502,7 +15503,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -15579,7 +15580,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -15656,7 +15657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -15733,7 +15734,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -15810,7 +15811,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>214</v>
       </c>
@@ -15887,7 +15888,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>217</v>
       </c>
@@ -15964,7 +15965,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -16041,7 +16042,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -16118,7 +16119,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -16195,7 +16196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -16272,7 +16273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -16349,7 +16350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>217</v>
       </c>
@@ -16426,7 +16427,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>218</v>
       </c>
@@ -16503,7 +16504,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -16580,7 +16581,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -16657,7 +16658,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -16734,7 +16735,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -16811,7 +16812,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -16888,7 +16889,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>218</v>
       </c>
@@ -16965,7 +16966,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>225</v>
       </c>
@@ -17040,7 +17041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -17117,7 +17118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -17192,7 +17193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -17269,7 +17270,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -17346,7 +17347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -17423,7 +17424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>225</v>
       </c>
@@ -17500,7 +17501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>239</v>
       </c>
@@ -17577,7 +17578,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>239</v>
       </c>
@@ -17654,7 +17655,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>239</v>
       </c>
@@ -17731,7 +17732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>239</v>
       </c>
@@ -17806,7 +17807,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>239</v>
       </c>
@@ -17883,7 +17884,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>239</v>
       </c>
@@ -17960,7 +17961,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>241</v>
       </c>
@@ -18029,7 +18030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>434</v>
       </c>
@@ -18104,7 +18105,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -18181,7 +18182,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -18258,7 +18259,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -18335,7 +18336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -18412,7 +18413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -18489,7 +18490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>434</v>
       </c>
@@ -18566,7 +18567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>436</v>
       </c>
@@ -18643,7 +18644,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -18720,7 +18721,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>436</v>
       </c>
@@ -18797,7 +18798,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>485</v>
       </c>
@@ -18870,7 +18871,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -18942,7 +18943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -19016,7 +19017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -19090,7 +19091,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -19164,7 +19165,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -19238,7 +19239,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -19312,7 +19313,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -19386,7 +19387,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -19460,7 +19461,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>485</v>
       </c>
@@ -19534,7 +19535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>488</v>
       </c>
@@ -19609,7 +19610,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -19683,7 +19684,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -19757,7 +19758,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -19831,7 +19832,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -19905,7 +19906,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -19979,7 +19980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -20053,7 +20054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -20127,7 +20128,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -20201,7 +20202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>488</v>
       </c>
@@ -20275,7 +20276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>509</v>
       </c>
@@ -20336,7 +20337,7 @@
         <v>99.45</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>509</v>
       </c>
@@ -20410,7 +20411,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>509</v>
       </c>
@@ -20484,7 +20485,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>509</v>
       </c>
@@ -20558,7 +20559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>509</v>
       </c>
@@ -20632,7 +20633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>509</v>
       </c>
@@ -20706,7 +20707,7 @@
         <v>98.77</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>509</v>
       </c>
@@ -20780,7 +20781,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>509</v>
       </c>
@@ -20854,7 +20855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>509</v>
       </c>
@@ -20928,7 +20929,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>509</v>
       </c>
@@ -21002,7 +21003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>509</v>
       </c>
@@ -21076,7 +21077,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>509</v>
       </c>
@@ -21150,7 +21151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>509</v>
       </c>
@@ -21224,7 +21225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>509</v>
       </c>
@@ -21298,7 +21299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>509</v>
       </c>
@@ -21372,7 +21373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>509</v>
       </c>
@@ -21446,7 +21447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>509</v>
       </c>
@@ -21520,7 +21521,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>509</v>
       </c>
@@ -21594,7 +21595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>509</v>
       </c>
@@ -21668,7 +21669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>68</v>
       </c>
@@ -21743,7 +21744,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>73</v>
       </c>
@@ -21820,7 +21821,7 @@
         <v>18.41</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>74</v>
       </c>
@@ -21897,7 +21898,7 @@
         <v>80.327868852459019</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>86</v>
       </c>
@@ -21974,7 +21975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>95</v>
       </c>
@@ -22051,7 +22052,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>143</v>
       </c>
@@ -22128,7 +22129,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>145</v>
       </c>
@@ -22205,7 +22206,7 @@
         <v>1.545454545454545</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>146</v>
       </c>
@@ -22282,7 +22283,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>148</v>
       </c>
@@ -22359,7 +22360,7 @@
         <v>1.977873977873978</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>159</v>
       </c>
@@ -22409,7 +22410,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>167</v>
       </c>
@@ -22480,7 +22481,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>193</v>
       </c>
@@ -22545,7 +22546,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>199</v>
       </c>
@@ -22614,7 +22615,7 @@
       <c r="X265" s="3"/>
       <c r="Y265" s="3"/>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>203</v>
       </c>
@@ -22691,7 +22692,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -22768,7 +22769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -22845,7 +22846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>203</v>
       </c>
@@ -22922,7 +22923,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>204</v>
       </c>
@@ -22987,7 +22988,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>205</v>
       </c>
@@ -23052,7 +23053,7 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>207</v>
       </c>
@@ -23117,7 +23118,7 @@
       <c r="X272" s="3"/>
       <c r="Y272" s="3"/>
     </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>215</v>
       </c>
@@ -23194,7 +23195,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -23271,7 +23272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -23348,7 +23349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -23425,7 +23426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -23502,7 +23503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -23579,7 +23580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>215</v>
       </c>
@@ -23656,7 +23657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>219</v>
       </c>
@@ -23731,7 +23732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -23808,7 +23809,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -23885,7 +23886,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -23962,7 +23963,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -24039,7 +24040,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -24116,7 +24117,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -24193,7 +24194,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>219</v>
       </c>
@@ -24251,7 +24252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>220</v>
       </c>
@@ -24326,7 +24327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -24403,7 +24404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -24480,7 +24481,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -24557,7 +24558,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -24634,7 +24635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -24707,7 +24708,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>220</v>
       </c>
@@ -24784,7 +24785,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>230</v>
       </c>
@@ -24847,7 +24848,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>231</v>
       </c>
@@ -24910,7 +24911,7 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>232</v>
       </c>
@@ -24973,7 +24974,7 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>245</v>
       </c>
@@ -25038,7 +25039,7 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>246</v>
       </c>
@@ -25101,7 +25102,7 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>252</v>
       </c>
@@ -25166,7 +25167,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>256</v>
       </c>
@@ -25229,7 +25230,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>260</v>
       </c>
@@ -25294,7 +25295,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>261</v>
       </c>
@@ -25359,7 +25360,7 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
     </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>262</v>
       </c>
@@ -25422,7 +25423,7 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>268</v>
       </c>
@@ -25487,7 +25488,7 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
     </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>269</v>
       </c>
@@ -25552,7 +25553,7 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>270</v>
       </c>
@@ -25617,7 +25618,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>271</v>
       </c>
@@ -25682,7 +25683,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>273</v>
       </c>
@@ -25747,7 +25748,7 @@
       <c r="X309" s="3"/>
       <c r="Y309" s="3"/>
     </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>274</v>
       </c>
@@ -25824,7 +25825,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -25901,7 +25902,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -25978,7 +25979,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -26055,7 +26056,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>274</v>
       </c>
@@ -26132,7 +26133,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>275</v>
       </c>
@@ -26209,7 +26210,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -26286,7 +26287,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -26363,7 +26364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>275</v>
       </c>
@@ -26440,7 +26441,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>276</v>
       </c>
@@ -26505,7 +26506,7 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
     </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>277</v>
       </c>
@@ -26570,7 +26571,7 @@
       <c r="X320" s="3"/>
       <c r="Y320" s="3"/>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>278</v>
       </c>
@@ -26647,7 +26648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>278</v>
       </c>
@@ -26724,7 +26725,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>278</v>
       </c>
@@ -26801,7 +26802,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>278</v>
       </c>
@@ -26878,7 +26879,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>282</v>
       </c>
@@ -26943,7 +26944,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>283</v>
       </c>
@@ -27008,7 +27009,7 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
     </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>285</v>
       </c>
@@ -27073,7 +27074,7 @@
       <c r="X327" s="3"/>
       <c r="Y327" s="3"/>
     </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>286</v>
       </c>
@@ -27150,7 +27151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>286</v>
       </c>
@@ -27227,7 +27228,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>286</v>
       </c>
@@ -27304,7 +27305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>286</v>
       </c>
@@ -27381,7 +27382,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>286</v>
       </c>
@@ -27458,7 +27459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>292</v>
       </c>
@@ -27535,7 +27536,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -27612,7 +27613,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -27689,7 +27690,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>292</v>
       </c>
@@ -27766,7 +27767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>294</v>
       </c>
@@ -27843,7 +27844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -27920,7 +27921,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -27997,7 +27998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>294</v>
       </c>
@@ -28074,7 +28075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>302</v>
       </c>
@@ -28151,7 +28152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>302</v>
       </c>
@@ -28228,7 +28229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>302</v>
       </c>
@@ -28305,7 +28306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>302</v>
       </c>
@@ -28382,7 +28383,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>302</v>
       </c>
@@ -28459,7 +28460,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>303</v>
       </c>
@@ -28534,7 +28535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -28611,7 +28612,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -28688,7 +28689,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>303</v>
       </c>
@@ -28765,7 +28766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>304</v>
       </c>
@@ -28830,7 +28831,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>323</v>
       </c>
@@ -28895,7 +28896,7 @@
       <c r="X351" s="3"/>
       <c r="Y351" s="3"/>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>324</v>
       </c>
@@ -28960,7 +28961,7 @@
       <c r="X352" s="3"/>
       <c r="Y352" s="3"/>
     </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>325</v>
       </c>
@@ -29025,7 +29026,7 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>327</v>
       </c>
@@ -29090,7 +29091,7 @@
       <c r="X354" s="3"/>
       <c r="Y354" s="3"/>
     </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>332</v>
       </c>
@@ -29155,7 +29156,7 @@
       <c r="X355" s="3"/>
       <c r="Y355" s="3"/>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>337</v>
       </c>
@@ -29220,7 +29221,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>338</v>
       </c>
@@ -29285,7 +29286,7 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>341</v>
       </c>
@@ -29350,7 +29351,7 @@
       <c r="X358" s="3"/>
       <c r="Y358" s="3"/>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>344</v>
       </c>
@@ -29415,7 +29416,7 @@
       <c r="X359" s="3"/>
       <c r="Y359" s="3"/>
     </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>356</v>
       </c>
@@ -29480,7 +29481,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>357</v>
       </c>
@@ -29541,7 +29542,7 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>358</v>
       </c>
@@ -29606,7 +29607,7 @@
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>359</v>
       </c>
@@ -29667,7 +29668,7 @@
       <c r="X363" s="3"/>
       <c r="Y363" s="3"/>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>362</v>
       </c>
@@ -29744,7 +29745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -29821,7 +29822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>362</v>
       </c>
@@ -29898,7 +29899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>363</v>
       </c>
@@ -29961,7 +29962,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>364</v>
       </c>
@@ -30026,7 +30027,7 @@
       <c r="X368" s="3"/>
       <c r="Y368" s="3"/>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>369</v>
       </c>
@@ -30103,7 +30104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -30180,7 +30181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>369</v>
       </c>
@@ -30257,7 +30258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>371</v>
       </c>
@@ -30322,7 +30323,7 @@
       <c r="X372" s="3"/>
       <c r="Y372" s="3"/>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>375</v>
       </c>
@@ -30399,7 +30400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -30476,7 +30477,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>375</v>
       </c>
@@ -30553,7 +30554,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>376</v>
       </c>
@@ -30618,7 +30619,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>379</v>
       </c>
@@ -30683,7 +30684,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>381</v>
       </c>
@@ -30748,7 +30749,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>382</v>
       </c>
@@ -30813,7 +30814,7 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>383</v>
       </c>
@@ -30878,7 +30879,7 @@
       <c r="X380" s="3"/>
       <c r="Y380" s="3"/>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>384</v>
       </c>
@@ -30943,7 +30944,7 @@
       <c r="X381" s="3"/>
       <c r="Y381" s="3"/>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>385</v>
       </c>
@@ -31008,7 +31009,7 @@
       <c r="X382" s="3"/>
       <c r="Y382" s="3"/>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>386</v>
       </c>
@@ -31085,7 +31086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -31162,7 +31163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -31239,7 +31240,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>386</v>
       </c>
@@ -31316,7 +31317,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>389</v>
       </c>
@@ -31389,7 +31390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -31463,7 +31464,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -31537,7 +31538,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -31611,7 +31612,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -31685,7 +31686,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -31759,7 +31760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -31833,7 +31834,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -31907,7 +31908,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -31981,7 +31982,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -32055,7 +32056,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -32129,7 +32130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -32203,7 +32204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>389</v>
       </c>
@@ -32277,7 +32278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>397</v>
       </c>
@@ -32342,7 +32343,7 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>398</v>
       </c>
@@ -32407,7 +32408,7 @@
       <c r="X401" s="3"/>
       <c r="Y401" s="3"/>
     </row>
-    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>399</v>
       </c>
@@ -32472,7 +32473,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>400</v>
       </c>
@@ -32537,7 +32538,7 @@
       <c r="X403" s="3"/>
       <c r="Y403" s="3"/>
     </row>
-    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>401</v>
       </c>
@@ -32602,7 +32603,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>403</v>
       </c>
@@ -32667,7 +32668,7 @@
       <c r="X405" s="3"/>
       <c r="Y405" s="3"/>
     </row>
-    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>408</v>
       </c>
@@ -32744,7 +32745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -32821,7 +32822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -32898,7 +32899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>408</v>
       </c>
@@ -32975,7 +32976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>422</v>
       </c>
@@ -33040,7 +33041,7 @@
       <c r="X410" s="3"/>
       <c r="Y410" s="3"/>
     </row>
-    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>426</v>
       </c>
@@ -33099,7 +33100,7 @@
       <c r="X411" s="3"/>
       <c r="Y411" s="3"/>
     </row>
-    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>427</v>
       </c>
@@ -33176,7 +33177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -33253,7 +33254,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -33330,7 +33331,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -33407,7 +33408,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -33484,7 +33485,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -33557,7 +33558,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>427</v>
       </c>
@@ -33634,7 +33635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>428</v>
       </c>
@@ -33711,7 +33712,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -33788,7 +33789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -33865,7 +33866,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -33940,7 +33941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -34017,7 +34018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -34090,7 +34091,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -34165,7 +34166,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>428</v>
       </c>
@@ -34219,7 +34220,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>429</v>
       </c>
@@ -34296,7 +34297,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -34373,7 +34374,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -34450,7 +34451,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -34527,7 +34528,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -34604,7 +34605,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -34681,7 +34682,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>429</v>
       </c>
@@ -34758,7 +34759,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>430</v>
       </c>
@@ -34835,7 +34836,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -34912,7 +34913,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -34989,7 +34990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -35066,7 +35067,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>430</v>
       </c>
@@ -35143,7 +35144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>433</v>
       </c>
@@ -35220,7 +35221,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -35297,7 +35298,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -35374,7 +35375,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -35451,7 +35452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -35524,7 +35525,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -35595,7 +35596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -35670,7 +35671,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>433</v>
       </c>
@@ -35728,7 +35729,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>435</v>
       </c>
@@ -35803,7 +35804,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -35880,7 +35881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -35957,7 +35958,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -36034,7 +36035,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -36111,7 +36112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -36188,7 +36189,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>435</v>
       </c>
@@ -36265,7 +36266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>439</v>
       </c>
@@ -36342,7 +36343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -36419,7 +36420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>439</v>
       </c>
@@ -36496,7 +36497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>440</v>
       </c>
@@ -36573,7 +36574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -36650,7 +36651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>440</v>
       </c>
@@ -36727,7 +36728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>444</v>
       </c>
@@ -36786,7 +36787,7 @@
       <c r="X460" s="3"/>
       <c r="Y460" s="3"/>
     </row>
-    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>445</v>
       </c>
@@ -36847,7 +36848,7 @@
       <c r="X461" s="3"/>
       <c r="Y461" s="3"/>
     </row>
-    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>447</v>
       </c>
@@ -36908,7 +36909,7 @@
       <c r="X462" s="3"/>
       <c r="Y462" s="3"/>
     </row>
-    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>448</v>
       </c>
@@ -36969,7 +36970,7 @@
       <c r="X463" s="3"/>
       <c r="Y463" s="3"/>
     </row>
-    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>451</v>
       </c>
@@ -37030,7 +37031,7 @@
       <c r="X464" s="3"/>
       <c r="Y464" s="3"/>
     </row>
-    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>452</v>
       </c>
@@ -37087,7 +37088,7 @@
       <c r="X465" s="3"/>
       <c r="Y465" s="3"/>
     </row>
-    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>466</v>
       </c>
@@ -37148,7 +37149,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
     </row>
-    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>467</v>
       </c>
@@ -37209,7 +37210,7 @@
       <c r="X467" s="3"/>
       <c r="Y467" s="3"/>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>468</v>
       </c>
@@ -37578,7 +37579,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>474</v>
       </c>
@@ -37651,7 +37652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -37725,7 +37726,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -37799,7 +37800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -37873,7 +37874,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -37947,7 +37948,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -38021,7 +38022,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -38095,7 +38096,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -38169,7 +38170,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -38243,7 +38244,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -38317,7 +38318,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -38391,7 +38392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -38465,7 +38466,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>474</v>
       </c>
@@ -38539,7 +38540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>475</v>
       </c>
@@ -38600,7 +38601,7 @@
       <c r="X486" s="3"/>
       <c r="Y486" s="3"/>
     </row>
-    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>476</v>
       </c>
@@ -38677,7 +38678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -38754,7 +38755,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -38831,7 +38832,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>476</v>
       </c>
@@ -38908,7 +38909,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>477</v>
       </c>
@@ -38979,7 +38980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -39053,7 +39054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -39127,7 +39128,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -39201,7 +39202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -39275,7 +39276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -39349,7 +39350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -39423,7 +39424,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -39497,7 +39498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -39571,7 +39572,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -39645,7 +39646,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -39719,7 +39720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -39793,7 +39794,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>477</v>
       </c>
@@ -39867,7 +39868,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>478</v>
       </c>
@@ -39940,7 +39941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -40014,7 +40015,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -40088,7 +40089,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -40162,7 +40163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -40236,7 +40237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -40310,7 +40311,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -40384,7 +40385,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -40458,7 +40459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -40532,7 +40533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -40606,7 +40607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -40680,7 +40681,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -40754,7 +40755,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>478</v>
       </c>
@@ -40828,7 +40829,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>479</v>
       </c>
@@ -40901,7 +40902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -40978,7 +40979,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -41055,7 +41056,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -41132,7 +41133,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -41209,7 +41210,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -41286,7 +41287,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -41363,7 +41364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -41440,7 +41441,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -41517,7 +41518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -41594,7 +41595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -41671,7 +41672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -41748,7 +41749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>479</v>
       </c>
@@ -41825,7 +41826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>480</v>
       </c>
@@ -41898,7 +41899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -41975,7 +41976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -42052,7 +42053,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -42129,7 +42130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -42206,7 +42207,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -42283,7 +42284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -42360,7 +42361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -42437,7 +42438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -42514,7 +42515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -42591,7 +42592,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -42668,7 +42669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -42745,7 +42746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>480</v>
       </c>
@@ -42822,7 +42823,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>481</v>
       </c>
@@ -42883,7 +42884,7 @@
       <c r="X543" s="3"/>
       <c r="Y543" s="3"/>
     </row>
-    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>481</v>
       </c>
@@ -42953,7 +42954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>486</v>
       </c>
@@ -43012,7 +43013,7 @@
       <c r="X545" s="3"/>
       <c r="Y545" s="3"/>
     </row>
-    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>506</v>
       </c>
@@ -43071,7 +43072,7 @@
       <c r="X546" s="3"/>
       <c r="Y546" s="3"/>
     </row>
-    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>507</v>
       </c>
@@ -43130,7 +43131,7 @@
       <c r="X547" s="3"/>
       <c r="Y547" s="3"/>
     </row>
-    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>514</v>
       </c>
@@ -43187,7 +43188,7 @@
       <c r="X548" s="3"/>
       <c r="Y548" s="3"/>
     </row>
-    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>515</v>
       </c>
@@ -43242,7 +43243,7 @@
       <c r="X549" s="3"/>
       <c r="Y549" s="3"/>
     </row>
-    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>516</v>
       </c>
@@ -43297,7 +43298,7 @@
       <c r="X550" s="3"/>
       <c r="Y550" s="3"/>
     </row>
-    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>519</v>
       </c>
@@ -43374,7 +43375,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -43451,7 +43452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>519</v>
       </c>
@@ -43528,7 +43529,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>523</v>
       </c>
@@ -43605,7 +43606,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -43682,7 +43683,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -43759,7 +43760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>523</v>
       </c>
@@ -43836,7 +43837,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>524</v>
       </c>
@@ -43913,7 +43914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -43990,7 +43991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="560" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -44067,7 +44068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -44144,7 +44145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -44221,7 +44222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="563" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -44298,7 +44299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>524</v>
       </c>
@@ -44375,7 +44376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="565" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>530</v>
       </c>
@@ -44430,7 +44431,7 @@
       <c r="X565" s="3"/>
       <c r="Y565" s="3"/>
     </row>
-    <row r="566" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>531</v>
       </c>
@@ -44485,7 +44486,7 @@
       <c r="X566" s="3"/>
       <c r="Y566" s="3"/>
     </row>
-    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>532</v>
       </c>
@@ -44554,7 +44555,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -44631,7 +44632,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -44708,7 +44709,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -44785,7 +44786,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>532</v>
       </c>
@@ -44862,7 +44863,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>533</v>
       </c>
@@ -44939,7 +44940,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -45016,7 +45017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>533</v>
       </c>
@@ -45093,7 +45094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>534</v>
       </c>
@@ -45170,7 +45171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -45247,7 +45248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>534</v>
       </c>
@@ -45324,7 +45325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>535</v>
       </c>
@@ -45401,7 +45402,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -45478,7 +45479,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>535</v>
       </c>
@@ -45555,7 +45556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>536</v>
       </c>
@@ -45632,7 +45633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -45709,7 +45710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>536</v>
       </c>
@@ -45786,7 +45787,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>537</v>
       </c>
@@ -45843,7 +45844,7 @@
       <c r="X584" s="3"/>
       <c r="Y584" s="3"/>
     </row>
-    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>538</v>
       </c>
@@ -45898,7 +45899,7 @@
       <c r="X585" s="3"/>
       <c r="Y585" s="3"/>
     </row>
-    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>539</v>
       </c>
@@ -45953,7 +45954,7 @@
       <c r="X586" s="3"/>
       <c r="Y586" s="3"/>
     </row>
-    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>540</v>
       </c>
@@ -46010,7 +46011,7 @@
       <c r="X587" s="3"/>
       <c r="Y587" s="3"/>
     </row>
-    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>543</v>
       </c>
@@ -46085,7 +46086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -46162,7 +46163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>543</v>
       </c>
@@ -46239,7 +46240,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>544</v>
       </c>
@@ -46314,7 +46315,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -46391,7 +46392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -46468,7 +46469,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -46545,7 +46546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>544</v>
       </c>
@@ -46622,7 +46623,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>550</v>
       </c>
@@ -46679,7 +46680,7 @@
       <c r="X596" s="3"/>
       <c r="Y596" s="3"/>
     </row>
-    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>551</v>
       </c>
@@ -46736,7 +46737,7 @@
       <c r="X597" s="3"/>
       <c r="Y597" s="3"/>
     </row>
-    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>554</v>
       </c>
@@ -46791,7 +46792,7 @@
       <c r="X598" s="3"/>
       <c r="Y598" s="3"/>
     </row>
-    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>555</v>
       </c>
@@ -46846,7 +46847,7 @@
       <c r="X599" s="3"/>
       <c r="Y599" s="3"/>
     </row>
-    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>69</v>
       </c>
@@ -46923,7 +46924,7 @@
         <v>90.541781450871994</v>
       </c>
     </row>
-    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>111</v>
       </c>
@@ -47000,7 +47001,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>197</v>
       </c>
@@ -47077,7 +47078,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>213</v>
       </c>
@@ -47154,7 +47155,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -47231,7 +47232,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -47308,7 +47309,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -47385,7 +47386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -47462,7 +47463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -47539,7 +47540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -47616,7 +47617,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -47693,7 +47694,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>213</v>
       </c>
@@ -47770,7 +47771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>233</v>
       </c>
@@ -47845,7 +47846,7 @@
         <v>64.367816091954026</v>
       </c>
     </row>
-    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>234</v>
       </c>
@@ -47920,7 +47921,7 @@
         <v>3692.25</v>
       </c>
     </row>
-    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>238</v>
       </c>
@@ -47993,7 +47994,7 @@
         <v>94.444444444444443</v>
       </c>
     </row>
-    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -48070,7 +48071,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -48147,7 +48148,7 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -48224,7 +48225,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -48301,7 +48302,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -48378,7 +48379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -48455,7 +48456,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -48532,7 +48533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>238</v>
       </c>
@@ -48609,7 +48610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>240</v>
       </c>
@@ -48684,7 +48685,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>251</v>
       </c>
@@ -48759,7 +48760,7 @@
       </c>
       <c r="Y624" s="3"/>
     </row>
-    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>254</v>
       </c>
@@ -48815,7 +48816,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>263</v>
       </c>
@@ -48892,7 +48893,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>265</v>
       </c>
@@ -48969,7 +48970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>266</v>
       </c>
@@ -49046,7 +49047,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>300</v>
       </c>
@@ -49123,7 +49124,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>301</v>
       </c>
@@ -49200,7 +49201,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>306</v>
       </c>
@@ -49275,7 +49276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -49352,7 +49353,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -49429,7 +49430,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -49506,7 +49507,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -49583,7 +49584,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -49660,7 +49661,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>306</v>
       </c>
@@ -49737,7 +49738,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>347</v>
       </c>
@@ -49814,7 +49815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>348</v>
       </c>
@@ -49891,7 +49892,7 @@
         <v>99.936143039591002</v>
       </c>
     </row>
-    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>351</v>
       </c>
@@ -49966,7 +49967,7 @@
         <v>11.41868512110727</v>
       </c>
     </row>
-    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>352</v>
       </c>
@@ -50041,7 +50042,7 @@
         <v>1.0385968556480199E-2</v>
       </c>
     </row>
-    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>368</v>
       </c>
@@ -50114,7 +50115,7 @@
       <c r="X642" s="3"/>
       <c r="Y642" s="3"/>
     </row>
-    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>372</v>
       </c>
@@ -50187,7 +50188,7 @@
       <c r="X643" s="3"/>
       <c r="Y643" s="3"/>
     </row>
-    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>373</v>
       </c>
@@ -50264,7 +50265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -50341,7 +50342,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -50418,7 +50419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -50495,7 +50496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -50572,7 +50573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -50649,7 +50650,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>373</v>
       </c>
@@ -50726,7 +50727,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>390</v>
       </c>
@@ -50803,7 +50804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -50880,7 +50881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -50957,7 +50958,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -51034,7 +51035,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -51111,7 +51112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -51188,7 +51189,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -51265,7 +51266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -51342,7 +51343,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -51419,7 +51420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -51496,7 +51497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -51573,7 +51574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -51650,7 +51651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>390</v>
       </c>
@@ -51727,7 +51728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>394</v>
       </c>
@@ -51804,7 +51805,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>395</v>
       </c>
@@ -51879,7 +51880,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>409</v>
       </c>
@@ -51950,7 +51951,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -52027,7 +52028,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>409</v>
       </c>
@@ -52104,7 +52105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>414</v>
       </c>
@@ -52181,7 +52182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -52258,7 +52259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -52335,7 +52336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -52412,7 +52413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -52489,7 +52490,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -52566,7 +52567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -52643,7 +52644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -52720,7 +52721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -52797,7 +52798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>414</v>
       </c>
@@ -52874,7 +52875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>415</v>
       </c>
@@ -52951,7 +52952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -53028,7 +53029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -53105,7 +53106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -53182,7 +53183,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -53259,7 +53260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -53336,7 +53337,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -53413,7 +53414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -53490,7 +53491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -53567,7 +53568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -53644,7 +53645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -53721,7 +53722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -53798,7 +53799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -53875,7 +53876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -53952,7 +53953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>415</v>
       </c>
@@ -54029,7 +54030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>416</v>
       </c>
@@ -54106,7 +54107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -54183,7 +54184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -54260,7 +54261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -54337,7 +54338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -54414,7 +54415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -54491,7 +54492,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700">
         <v>416</v>
       </c>
@@ -54568,7 +54569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>417</v>
       </c>
@@ -54645,7 +54646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -54722,7 +54723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -54799,7 +54800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -54876,7 +54877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -54953,7 +54954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -55030,7 +55031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707">
         <v>417</v>
       </c>
@@ -55107,7 +55108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>418</v>
       </c>
@@ -55184,7 +55185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -55261,7 +55262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -55338,7 +55339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -55415,7 +55416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -55490,7 +55491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -55567,7 +55568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -55644,7 +55645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -55721,7 +55722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -55798,7 +55799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717">
         <v>418</v>
       </c>
@@ -55875,7 +55876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>420</v>
       </c>
@@ -55952,7 +55953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -56029,7 +56030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -56106,7 +56107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -56183,7 +56184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -56260,7 +56261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -56337,7 +56338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724">
         <v>420</v>
       </c>
@@ -56414,7 +56415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>431</v>
       </c>
@@ -56487,7 +56488,7 @@
       <c r="X725" s="3"/>
       <c r="Y725" s="3"/>
     </row>
-    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>432</v>
       </c>
@@ -56564,7 +56565,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -56641,7 +56642,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -56718,7 +56719,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -56795,7 +56796,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -56872,7 +56873,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -56949,7 +56950,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -57026,7 +57027,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -57103,7 +57104,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -57180,7 +57181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735">
         <v>432</v>
       </c>
@@ -57257,7 +57258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>453</v>
       </c>
@@ -57326,7 +57327,7 @@
       <c r="X736" s="3"/>
       <c r="Y736" s="3"/>
     </row>
-    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>455</v>
       </c>
@@ -57391,7 +57392,7 @@
       <c r="X737" s="3"/>
       <c r="Y737" s="3"/>
     </row>
-    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>456</v>
       </c>
@@ -57462,7 +57463,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -57539,7 +57540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -57616,7 +57617,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741">
         <v>456</v>
       </c>
@@ -57693,7 +57694,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>457</v>
       </c>
@@ -57764,7 +57765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -57841,7 +57842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -57918,7 +57919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745">
         <v>457</v>
       </c>
@@ -57995,7 +57996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>469</v>
       </c>
@@ -58070,7 +58071,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -58147,7 +58148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -58224,7 +58225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -58301,7 +58302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -58378,7 +58379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -58455,7 +58456,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -58532,7 +58533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -58609,7 +58610,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -58686,7 +58687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -58763,7 +58764,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756">
         <v>469</v>
       </c>
@@ -58840,7 +58841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>470</v>
       </c>
@@ -58917,7 +58918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -58992,7 +58993,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -59069,7 +59070,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -59146,7 +59147,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -59223,7 +59224,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762">
         <v>470</v>
       </c>
@@ -59300,7 +59301,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>471</v>
       </c>
@@ -59377,7 +59378,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -59454,7 +59455,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -59531,7 +59532,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -59608,7 +59609,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -59685,7 +59686,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -59762,7 +59763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -59839,7 +59840,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="770" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770">
         <v>471</v>
       </c>
@@ -59916,7 +59917,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="771" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>484</v>
       </c>
@@ -59983,7 +59984,7 @@
       <c r="X771" s="3"/>
       <c r="Y771" s="3"/>
     </row>
-    <row r="772" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
         <v>510</v>
       </c>
@@ -60058,7 +60059,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="773" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773">
         <v>510</v>
       </c>
@@ -60129,7 +60130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="774" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774" s="1">
         <v>511</v>
       </c>
@@ -60204,7 +60205,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -60281,7 +60282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="776" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -60358,7 +60359,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="777" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -60435,7 +60436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="778" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -60512,7 +60513,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="779" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -60589,7 +60590,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="780" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -60666,7 +60667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="781" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781">
         <v>511</v>
       </c>
@@ -60743,7 +60744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="782" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>513</v>
       </c>
@@ -60804,7 +60805,7 @@
       <c r="X782" s="3"/>
       <c r="Y782" s="3"/>
     </row>
-    <row r="783" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>518</v>
       </c>
@@ -60858,7 +60859,7 @@
       </c>
       <c r="R783" s="3"/>
     </row>
-    <row r="784" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>526</v>
       </c>
@@ -60915,7 +60916,7 @@
       <c r="X784" s="3"/>
       <c r="Y784" s="3"/>
     </row>
-    <row r="785" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>529</v>
       </c>
@@ -60990,7 +60991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="786" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -61067,7 +61068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="787" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A787">
         <v>529</v>
       </c>
@@ -61146,6 +61147,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:Y787" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="473"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C511EDA4-3599-463F-9AB9-94CD6B5E27D0}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F07097AB-2D91-4FA1-9188-7455D710DADA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -61086,6 +61086,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F07097AB-2D91-4FA1-9188-7455D710DADA}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2CC6436-6B0C-447F-A43E-462499B5B096}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -4020,6 +4020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4104,7 +4105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -4174,7 +4175,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -4244,7 +4245,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -4314,7 +4315,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -4384,7 +4385,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -4454,7 +4455,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -4524,7 +4525,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -4594,7 +4595,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -4664,7 +4665,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -4734,7 +4735,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -4804,7 +4805,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -4874,7 +4875,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -4944,7 +4945,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -5011,7 +5012,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -5080,7 +5081,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -5149,7 +5150,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -5218,7 +5219,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -5287,7 +5288,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -5348,7 +5349,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -5417,7 +5418,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -5486,7 +5487,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -5556,7 +5557,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -5626,7 +5627,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -5693,7 +5694,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -5757,7 +5758,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -5817,7 +5818,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -5880,7 +5881,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -5945,7 +5946,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -6007,7 +6008,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -6065,7 +6066,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -6123,7 +6124,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -6197,7 +6198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -6271,7 +6272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -6345,7 +6346,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -6419,7 +6420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -6493,7 +6494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -6567,7 +6568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -6641,7 +6642,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>221</v>
       </c>
@@ -6705,7 +6706,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -6779,7 +6780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -6853,7 +6854,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -6927,7 +6928,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -7001,7 +7002,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -7075,7 +7076,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -7149,7 +7150,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>222</v>
       </c>
@@ -7223,7 +7224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -7297,7 +7298,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -7369,7 +7370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -7443,7 +7444,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -7517,7 +7518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -7577,7 +7578,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -7651,7 +7652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -7725,7 +7726,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -7799,7 +7800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -7871,7 +7872,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -7945,7 +7946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -8019,7 +8020,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -8091,7 +8092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -8165,7 +8166,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -8239,7 +8240,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -8313,7 +8314,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -8387,7 +8388,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -8461,7 +8462,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -8535,7 +8536,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -8607,7 +8608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -8681,7 +8682,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -8751,7 +8752,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -8825,7 +8826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -8895,7 +8896,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -8965,7 +8966,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -9039,7 +9040,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -9111,7 +9112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -9185,7 +9186,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -9259,7 +9260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -9333,7 +9334,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -9407,7 +9408,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -9481,7 +9482,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -9555,7 +9556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -9612,7 +9613,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -9668,7 +9669,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -9736,7 +9737,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -9798,7 +9799,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -9872,7 +9873,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -9946,7 +9947,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -10020,7 +10021,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -10094,7 +10095,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -10168,7 +10169,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -10242,7 +10243,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -10304,7 +10305,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -10363,7 +10364,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -10479,7 +10480,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -10539,7 +10540,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -10595,7 +10596,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -10653,7 +10654,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -10711,7 +10712,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -10767,7 +10768,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -10825,7 +10826,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -10883,7 +10884,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>367</v>
       </c>
@@ -10941,7 +10942,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -10999,7 +11000,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -11057,7 +11058,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -11113,7 +11114,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -11169,7 +11170,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -11225,7 +11226,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -11283,7 +11284,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -11341,7 +11342,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -11399,7 +11400,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -11455,7 +11456,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -11511,7 +11512,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -11567,7 +11568,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>491</v>
       </c>
@@ -11623,7 +11624,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -11679,7 +11680,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -11735,7 +11736,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -11791,7 +11792,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>495</v>
       </c>
@@ -11847,7 +11848,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -11903,7 +11904,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>498</v>
       </c>
@@ -11959,7 +11960,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>499</v>
       </c>
@@ -12013,7 +12014,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>500</v>
       </c>
@@ -12069,7 +12070,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>501</v>
       </c>
@@ -12125,7 +12126,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>502</v>
       </c>
@@ -12181,7 +12182,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>503</v>
       </c>
@@ -12237,7 +12238,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>504</v>
       </c>
@@ -12293,7 +12294,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>505</v>
       </c>
@@ -12349,7 +12350,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>508</v>
       </c>
@@ -12405,7 +12406,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>522</v>
       </c>
@@ -12459,7 +12460,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>527</v>
       </c>
@@ -12511,7 +12512,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>528</v>
       </c>
@@ -12566,7 +12567,7 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>541</v>
       </c>
@@ -12980,7 +12981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>546</v>
       </c>
@@ -13042,7 +13043,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>546</v>
       </c>
@@ -13113,7 +13114,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -13184,7 +13185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -13255,7 +13256,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>547</v>
       </c>
@@ -13309,7 +13310,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>552</v>
       </c>
@@ -13363,7 +13364,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>553</v>
       </c>
@@ -13417,7 +13418,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>556</v>
       </c>
@@ -13471,7 +13472,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>290</v>
       </c>
@@ -13544,7 +13545,7 @@
         <v>91.666666666666657</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>290</v>
       </c>
@@ -13618,7 +13619,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -13692,7 +13693,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -13766,7 +13767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -13840,7 +13841,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -13914,7 +13915,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -13988,7 +13989,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -14062,7 +14063,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -14136,7 +14137,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -14210,7 +14211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>77</v>
       </c>
@@ -14287,7 +14288,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>121</v>
       </c>
@@ -14364,7 +14365,7 @@
         <v>99.18</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>122</v>
       </c>
@@ -14441,7 +14442,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>124</v>
       </c>
@@ -14518,7 +14519,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>125</v>
       </c>
@@ -14595,7 +14596,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>128</v>
       </c>
@@ -14672,7 +14673,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>172</v>
       </c>
@@ -14749,7 +14750,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>208</v>
       </c>
@@ -14826,7 +14827,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>208</v>
       </c>
@@ -14903,7 +14904,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -14980,7 +14981,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -15057,7 +15058,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -15134,7 +15135,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -15211,7 +15212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -15288,7 +15289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>214</v>
       </c>
@@ -15365,7 +15366,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>214</v>
       </c>
@@ -15442,7 +15443,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -15519,7 +15520,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -15596,7 +15597,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -15673,7 +15674,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -15750,7 +15751,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -15827,7 +15828,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>217</v>
       </c>
@@ -15904,7 +15905,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>217</v>
       </c>
@@ -15981,7 +15982,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -16058,7 +16059,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -16135,7 +16136,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -16212,7 +16213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -16289,7 +16290,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -16366,7 +16367,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>218</v>
       </c>
@@ -16443,7 +16444,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>218</v>
       </c>
@@ -16520,7 +16521,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -16597,7 +16598,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -16674,7 +16675,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -16751,7 +16752,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -16828,7 +16829,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -16905,7 +16906,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>225</v>
       </c>
@@ -16980,7 +16981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>225</v>
       </c>
@@ -17057,7 +17058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -17132,7 +17133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -17209,7 +17210,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -17286,7 +17287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -17363,7 +17364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -17900,7 +17901,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>241</v>
       </c>
@@ -17969,7 +17970,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>434</v>
       </c>
@@ -18044,7 +18045,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>434</v>
       </c>
@@ -18121,7 +18122,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -18198,7 +18199,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -18275,7 +18276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -18352,7 +18353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -18429,7 +18430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -18506,7 +18507,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>436</v>
       </c>
@@ -18583,7 +18584,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>436</v>
       </c>
@@ -18660,7 +18661,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -18737,7 +18738,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>485</v>
       </c>
@@ -18810,7 +18811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>485</v>
       </c>
@@ -18882,7 +18883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -18956,7 +18957,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -19030,7 +19031,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -19104,7 +19105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -19178,7 +19179,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -19252,7 +19253,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -19326,7 +19327,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -19400,7 +19401,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -19474,7 +19475,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>488</v>
       </c>
@@ -19549,7 +19550,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>488</v>
       </c>
@@ -19623,7 +19624,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -19697,7 +19698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -19771,7 +19772,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -19845,7 +19846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -19919,7 +19920,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -19993,7 +19994,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -20067,7 +20068,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -20141,7 +20142,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -20215,7 +20216,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>509</v>
       </c>
@@ -20276,7 +20277,7 @@
         <v>99.45</v>
       </c>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>509</v>
       </c>
@@ -20350,7 +20351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>509</v>
       </c>
@@ -20424,7 +20425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>509</v>
       </c>
@@ -20498,7 +20499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>509</v>
       </c>
@@ -20572,7 +20573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>509</v>
       </c>
@@ -20646,7 +20647,7 @@
         <v>98.77</v>
       </c>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>509</v>
       </c>
@@ -20720,7 +20721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>509</v>
       </c>
@@ -20794,7 +20795,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>509</v>
       </c>
@@ -20868,7 +20869,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>509</v>
       </c>
@@ -20942,7 +20943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>509</v>
       </c>
@@ -21016,7 +21017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>509</v>
       </c>
@@ -21090,7 +21091,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>509</v>
       </c>
@@ -21164,7 +21165,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>509</v>
       </c>
@@ -21238,7 +21239,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>509</v>
       </c>
@@ -21312,7 +21313,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>509</v>
       </c>
@@ -21386,7 +21387,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>509</v>
       </c>
@@ -21460,7 +21461,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>509</v>
       </c>
@@ -21534,7 +21535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>509</v>
       </c>
@@ -21608,7 +21609,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>68</v>
       </c>
@@ -21683,7 +21684,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>73</v>
       </c>
@@ -21760,7 +21761,7 @@
         <v>18.41</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>74</v>
       </c>
@@ -21837,7 +21838,7 @@
         <v>80.327868852459019</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>86</v>
       </c>
@@ -21914,7 +21915,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>95</v>
       </c>
@@ -22068,7 +22069,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>145</v>
       </c>
@@ -22145,7 +22146,7 @@
         <v>1.545454545454545</v>
       </c>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>146</v>
       </c>
@@ -22222,7 +22223,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>148</v>
       </c>
@@ -22299,7 +22300,7 @@
         <v>1.977873977873978</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>159</v>
       </c>
@@ -22349,7 +22350,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>167</v>
       </c>
@@ -22420,7 +22421,7 @@
       <c r="X262" s="3"/>
       <c r="Y262" s="3"/>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>193</v>
       </c>
@@ -22485,7 +22486,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>199</v>
       </c>
@@ -22554,7 +22555,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>203</v>
       </c>
@@ -22631,7 +22632,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>203</v>
       </c>
@@ -22708,7 +22709,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -22785,7 +22786,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -22862,7 +22863,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>204</v>
       </c>
@@ -22927,7 +22928,7 @@
       <c r="X269" s="3"/>
       <c r="Y269" s="3"/>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>205</v>
       </c>
@@ -22992,7 +22993,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>207</v>
       </c>
@@ -23057,7 +23058,7 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>215</v>
       </c>
@@ -23134,7 +23135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>215</v>
       </c>
@@ -23211,7 +23212,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -23288,7 +23289,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -23365,7 +23366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -23442,7 +23443,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -23519,7 +23520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -23596,7 +23597,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>219</v>
       </c>
@@ -23671,7 +23672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>219</v>
       </c>
@@ -23748,7 +23749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -23825,7 +23826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -23902,7 +23903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -23979,7 +23980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -24056,7 +24057,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -24133,7 +24134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -24191,7 +24192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>220</v>
       </c>
@@ -24266,7 +24267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>220</v>
       </c>
@@ -24343,7 +24344,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -24420,7 +24421,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -24497,7 +24498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -24574,7 +24575,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -24647,7 +24648,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -24724,7 +24725,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>230</v>
       </c>
@@ -24787,7 +24788,7 @@
       <c r="X294" s="3"/>
       <c r="Y294" s="3"/>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>231</v>
       </c>
@@ -24850,7 +24851,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>232</v>
       </c>
@@ -24913,7 +24914,7 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>245</v>
       </c>
@@ -24978,7 +24979,7 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>246</v>
       </c>
@@ -25041,7 +25042,7 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>252</v>
       </c>
@@ -25106,7 +25107,7 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>256</v>
       </c>
@@ -25169,7 +25170,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>260</v>
       </c>
@@ -25234,7 +25235,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>261</v>
       </c>
@@ -25299,7 +25300,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>262</v>
       </c>
@@ -25622,7 +25623,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>273</v>
       </c>
@@ -25687,7 +25688,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>274</v>
       </c>
@@ -25764,7 +25765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>274</v>
       </c>
@@ -25841,7 +25842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -25918,7 +25919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -25995,7 +25996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -26072,7 +26073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>275</v>
       </c>
@@ -26149,7 +26150,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>275</v>
       </c>
@@ -26226,7 +26227,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -26303,7 +26304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -26380,7 +26381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>276</v>
       </c>
@@ -26445,7 +26446,7 @@
       <c r="X318" s="3"/>
       <c r="Y318" s="3"/>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>277</v>
       </c>
@@ -26818,7 +26819,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>282</v>
       </c>
@@ -26883,7 +26884,7 @@
       <c r="X324" s="3"/>
       <c r="Y324" s="3"/>
     </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>283</v>
       </c>
@@ -26948,7 +26949,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>285</v>
       </c>
@@ -27398,7 +27399,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>292</v>
       </c>
@@ -27475,7 +27476,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>292</v>
       </c>
@@ -27552,7 +27553,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -27629,7 +27630,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -27706,7 +27707,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>294</v>
       </c>
@@ -27783,7 +27784,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>294</v>
       </c>
@@ -27860,7 +27861,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -27937,7 +27938,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -28399,7 +28400,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>303</v>
       </c>
@@ -28474,7 +28475,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>303</v>
       </c>
@@ -28551,7 +28552,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -28628,7 +28629,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -28705,7 +28706,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>304</v>
       </c>
@@ -28770,7 +28771,7 @@
       <c r="X349" s="3"/>
       <c r="Y349" s="3"/>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>323</v>
       </c>
@@ -28835,7 +28836,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>324</v>
       </c>
@@ -29030,7 +29031,7 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>332</v>
       </c>
@@ -29225,7 +29226,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>341</v>
       </c>
@@ -29290,7 +29291,7 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>344</v>
       </c>
@@ -29355,7 +29356,7 @@
       <c r="X358" s="3"/>
       <c r="Y358" s="3"/>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>356</v>
       </c>
@@ -29481,7 +29482,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>358</v>
       </c>
@@ -29546,7 +29547,7 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>359</v>
       </c>
@@ -29607,7 +29608,7 @@
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -29684,7 +29685,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>362</v>
       </c>
@@ -29761,7 +29762,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -29838,7 +29839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>363</v>
       </c>
@@ -29901,7 +29902,7 @@
       <c r="X366" s="3"/>
       <c r="Y366" s="3"/>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>364</v>
       </c>
@@ -29966,7 +29967,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>369</v>
       </c>
@@ -30043,7 +30044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>369</v>
       </c>
@@ -30120,7 +30121,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -30197,7 +30198,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>371</v>
       </c>
@@ -30262,7 +30263,7 @@
       <c r="X371" s="3"/>
       <c r="Y371" s="3"/>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>375</v>
       </c>
@@ -30339,7 +30340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -30416,7 +30417,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -30493,7 +30494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>376</v>
       </c>
@@ -30558,7 +30559,7 @@
       <c r="X375" s="3"/>
       <c r="Y375" s="3"/>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>379</v>
       </c>
@@ -30623,7 +30624,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>381</v>
       </c>
@@ -30688,7 +30689,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>382</v>
       </c>
@@ -30753,7 +30754,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>383</v>
       </c>
@@ -30818,7 +30819,7 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>384</v>
       </c>
@@ -30883,7 +30884,7 @@
       <c r="X380" s="3"/>
       <c r="Y380" s="3"/>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>385</v>
       </c>
@@ -30948,7 +30949,7 @@
       <c r="X381" s="3"/>
       <c r="Y381" s="3"/>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>386</v>
       </c>
@@ -31025,7 +31026,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>386</v>
       </c>
@@ -31102,7 +31103,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -31179,7 +31180,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -31256,7 +31257,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>389</v>
       </c>
@@ -31329,7 +31330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -31403,7 +31404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -31477,7 +31478,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -31551,7 +31552,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -31625,7 +31626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -31699,7 +31700,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -31773,7 +31774,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -31847,7 +31848,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -31921,7 +31922,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -31995,7 +31996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -32069,7 +32070,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -32143,7 +32144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -32217,7 +32218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -32282,7 +32283,7 @@
       <c r="X399" s="3"/>
       <c r="Y399" s="3"/>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -32347,7 +32348,7 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -32412,7 +32413,7 @@
       <c r="X401" s="3"/>
       <c r="Y401" s="3"/>
     </row>
-    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -32477,7 +32478,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -32607,7 +32608,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>408</v>
       </c>
@@ -32684,7 +32685,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -32761,7 +32762,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -32838,7 +32839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -32915,7 +32916,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>422</v>
       </c>
@@ -32980,7 +32981,7 @@
       <c r="X409" s="3"/>
       <c r="Y409" s="3"/>
     </row>
-    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>426</v>
       </c>
@@ -33039,7 +33040,7 @@
       <c r="X410" s="3"/>
       <c r="Y410" s="3"/>
     </row>
-    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>427</v>
       </c>
@@ -33116,7 +33117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>427</v>
       </c>
@@ -33193,7 +33194,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -33270,7 +33271,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -33347,7 +33348,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -33424,7 +33425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -33497,7 +33498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -33574,7 +33575,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>428</v>
       </c>
@@ -33651,7 +33652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>428</v>
       </c>
@@ -33728,7 +33729,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -33805,7 +33806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -33880,7 +33881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -33957,7 +33958,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -34030,7 +34031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -34105,7 +34106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -34159,7 +34160,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>429</v>
       </c>
@@ -34236,7 +34237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -34313,7 +34314,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -34390,7 +34391,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -34467,7 +34468,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -34544,7 +34545,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -34621,7 +34622,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -34698,7 +34699,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>430</v>
       </c>
@@ -34775,7 +34776,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>430</v>
       </c>
@@ -34852,7 +34853,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -34929,7 +34930,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -35006,7 +35007,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -35083,7 +35084,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>433</v>
       </c>
@@ -35160,7 +35161,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>433</v>
       </c>
@@ -35237,7 +35238,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -35314,7 +35315,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -35391,7 +35392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -35464,7 +35465,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -35535,7 +35536,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -35610,7 +35611,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -35668,7 +35669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>435</v>
       </c>
@@ -35743,7 +35744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>435</v>
       </c>
@@ -35820,7 +35821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -35897,7 +35898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -35974,7 +35975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -36051,7 +36052,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -36128,7 +36129,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -36205,7 +36206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>439</v>
       </c>
@@ -36282,7 +36283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>439</v>
       </c>
@@ -36359,7 +36360,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -36436,7 +36437,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>440</v>
       </c>
@@ -36513,7 +36514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>440</v>
       </c>
@@ -36590,7 +36591,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -36667,7 +36668,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>444</v>
       </c>
@@ -36726,7 +36727,7 @@
       <c r="X459" s="3"/>
       <c r="Y459" s="3"/>
     </row>
-    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>445</v>
       </c>
@@ -36787,7 +36788,7 @@
       <c r="X460" s="3"/>
       <c r="Y460" s="3"/>
     </row>
-    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>447</v>
       </c>
@@ -36848,7 +36849,7 @@
       <c r="X461" s="3"/>
       <c r="Y461" s="3"/>
     </row>
-    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>448</v>
       </c>
@@ -36909,7 +36910,7 @@
       <c r="X462" s="3"/>
       <c r="Y462" s="3"/>
     </row>
-    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>451</v>
       </c>
@@ -36970,7 +36971,7 @@
       <c r="X463" s="3"/>
       <c r="Y463" s="3"/>
     </row>
-    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>452</v>
       </c>
@@ -37027,7 +37028,7 @@
       <c r="X464" s="3"/>
       <c r="Y464" s="3"/>
     </row>
-    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>466</v>
       </c>
@@ -37088,7 +37089,7 @@
       <c r="X465" s="3"/>
       <c r="Y465" s="3"/>
     </row>
-    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>467</v>
       </c>
@@ -37149,7 +37150,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
     </row>
-    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>468</v>
       </c>
@@ -37210,7 +37211,7 @@
       <c r="X467" s="3"/>
       <c r="Y467" s="3"/>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>473</v>
       </c>
@@ -37287,7 +37288,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -37364,7 +37365,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>473</v>
       </c>
@@ -37441,7 +37442,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>473</v>
       </c>
@@ -37518,7 +37519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>474</v>
       </c>
@@ -37591,7 +37592,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>474</v>
       </c>
@@ -37665,7 +37666,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -37739,7 +37740,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -37813,7 +37814,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -37887,7 +37888,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -37961,7 +37962,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -38035,7 +38036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -38109,7 +38110,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -38183,7 +38184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -38257,7 +38258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -38331,7 +38332,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -38405,7 +38406,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -38479,7 +38480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>475</v>
       </c>
@@ -38540,7 +38541,7 @@
       <c r="X485" s="3"/>
       <c r="Y485" s="3"/>
     </row>
-    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>476</v>
       </c>
@@ -38617,7 +38618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>476</v>
       </c>
@@ -38694,7 +38695,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -38771,7 +38772,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -38848,7 +38849,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>477</v>
       </c>
@@ -38919,7 +38920,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>477</v>
       </c>
@@ -38993,7 +38994,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -39067,7 +39068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -39141,7 +39142,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -39215,7 +39216,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -39289,7 +39290,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -39363,7 +39364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -39437,7 +39438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -39511,7 +39512,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -39585,7 +39586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -39659,7 +39660,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -39733,7 +39734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -39807,7 +39808,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>478</v>
       </c>
@@ -39880,7 +39881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>478</v>
       </c>
@@ -39954,7 +39955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -40028,7 +40029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -40102,7 +40103,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -40176,7 +40177,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -40250,7 +40251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -40324,7 +40325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -40398,7 +40399,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -40472,7 +40473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -40546,7 +40547,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -40620,7 +40621,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -40694,7 +40695,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -40768,7 +40769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>479</v>
       </c>
@@ -40841,7 +40842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>479</v>
       </c>
@@ -40918,7 +40919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -40995,7 +40996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -41072,7 +41073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -41149,7 +41150,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -41226,7 +41227,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -41303,7 +41304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -41380,7 +41381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -41457,7 +41458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -41534,7 +41535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -41611,7 +41612,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -41688,7 +41689,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -41765,7 +41766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>480</v>
       </c>
@@ -41838,7 +41839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>480</v>
       </c>
@@ -41915,7 +41916,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -41992,7 +41993,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -42069,7 +42070,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -42146,7 +42147,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -42223,7 +42224,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -42300,7 +42301,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -42377,7 +42378,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -42454,7 +42455,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -42531,7 +42532,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -42608,7 +42609,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -42685,7 +42686,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -42762,7 +42763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>481</v>
       </c>
@@ -42823,7 +42824,7 @@
       <c r="X542" s="3"/>
       <c r="Y542" s="3"/>
     </row>
-    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>481</v>
       </c>
@@ -42893,7 +42894,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>486</v>
       </c>
@@ -42952,7 +42953,7 @@
       <c r="X544" s="3"/>
       <c r="Y544" s="3"/>
     </row>
-    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>506</v>
       </c>
@@ -43011,7 +43012,7 @@
       <c r="X545" s="3"/>
       <c r="Y545" s="3"/>
     </row>
-    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>507</v>
       </c>
@@ -43070,7 +43071,7 @@
       <c r="X546" s="3"/>
       <c r="Y546" s="3"/>
     </row>
-    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>514</v>
       </c>
@@ -43127,7 +43128,7 @@
       <c r="X547" s="3"/>
       <c r="Y547" s="3"/>
     </row>
-    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>515</v>
       </c>
@@ -43182,7 +43183,7 @@
       <c r="X548" s="3"/>
       <c r="Y548" s="3"/>
     </row>
-    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>516</v>
       </c>
@@ -43237,7 +43238,7 @@
       <c r="X549" s="3"/>
       <c r="Y549" s="3"/>
     </row>
-    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>519</v>
       </c>
@@ -43314,7 +43315,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>519</v>
       </c>
@@ -43391,7 +43392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -43468,7 +43469,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>523</v>
       </c>
@@ -43545,7 +43546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>523</v>
       </c>
@@ -43622,7 +43623,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -43699,7 +43700,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -43776,7 +43777,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>524</v>
       </c>
@@ -43853,7 +43854,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>524</v>
       </c>
@@ -43930,7 +43931,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -44007,7 +44008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="560" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -44084,7 +44085,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -44161,7 +44162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -44238,7 +44239,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="563" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -44315,7 +44316,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>530</v>
       </c>
@@ -44370,7 +44371,7 @@
       <c r="X564" s="3"/>
       <c r="Y564" s="3"/>
     </row>
-    <row r="565" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>531</v>
       </c>
@@ -44425,7 +44426,7 @@
       <c r="X565" s="3"/>
       <c r="Y565" s="3"/>
     </row>
-    <row r="566" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>532</v>
       </c>
@@ -44494,7 +44495,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>532</v>
       </c>
@@ -44571,7 +44572,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -44648,7 +44649,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -44725,7 +44726,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -44802,7 +44803,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>533</v>
       </c>
@@ -44879,7 +44880,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>533</v>
       </c>
@@ -44956,7 +44957,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -45033,7 +45034,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>534</v>
       </c>
@@ -45110,7 +45111,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>534</v>
       </c>
@@ -45187,7 +45188,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -45264,7 +45265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>535</v>
       </c>
@@ -45341,7 +45342,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -45418,7 +45419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -45495,7 +45496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>536</v>
       </c>
@@ -45572,7 +45573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>536</v>
       </c>
@@ -45649,7 +45650,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -45726,7 +45727,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>537</v>
       </c>
@@ -45783,7 +45784,7 @@
       <c r="X583" s="3"/>
       <c r="Y583" s="3"/>
     </row>
-    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>538</v>
       </c>
@@ -45838,7 +45839,7 @@
       <c r="X584" s="3"/>
       <c r="Y584" s="3"/>
     </row>
-    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>539</v>
       </c>
@@ -45893,7 +45894,7 @@
       <c r="X585" s="3"/>
       <c r="Y585" s="3"/>
     </row>
-    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>540</v>
       </c>
@@ -45950,7 +45951,7 @@
       <c r="X586" s="3"/>
       <c r="Y586" s="3"/>
     </row>
-    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>543</v>
       </c>
@@ -46025,7 +46026,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>543</v>
       </c>
@@ -46102,7 +46103,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -46179,7 +46180,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>544</v>
       </c>
@@ -46254,7 +46255,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>544</v>
       </c>
@@ -46331,7 +46332,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -46408,7 +46409,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -46485,7 +46486,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -46562,7 +46563,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>550</v>
       </c>
@@ -46619,7 +46620,7 @@
       <c r="X595" s="3"/>
       <c r="Y595" s="3"/>
     </row>
-    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>551</v>
       </c>
@@ -46676,7 +46677,7 @@
       <c r="X596" s="3"/>
       <c r="Y596" s="3"/>
     </row>
-    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>554</v>
       </c>
@@ -46731,7 +46732,7 @@
       <c r="X597" s="3"/>
       <c r="Y597" s="3"/>
     </row>
-    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>555</v>
       </c>
@@ -46786,7 +46787,7 @@
       <c r="X598" s="3"/>
       <c r="Y598" s="3"/>
     </row>
-    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>69</v>
       </c>
@@ -46863,7 +46864,7 @@
         <v>90.541781450871994</v>
       </c>
     </row>
-    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>111</v>
       </c>
@@ -46940,7 +46941,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>197</v>
       </c>
@@ -47017,7 +47018,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>213</v>
       </c>
@@ -47094,7 +47095,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>213</v>
       </c>
@@ -47171,7 +47172,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -47248,7 +47249,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -47325,7 +47326,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -47402,7 +47403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -47479,7 +47480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -47556,7 +47557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -47633,7 +47634,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -47710,7 +47711,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>233</v>
       </c>
@@ -47785,7 +47786,7 @@
         <v>64.367816091954026</v>
       </c>
     </row>
-    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>234</v>
       </c>
@@ -47860,7 +47861,7 @@
         <v>3692.25</v>
       </c>
     </row>
-    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>238</v>
       </c>
@@ -47933,7 +47934,7 @@
         <v>94.444444444444443</v>
       </c>
     </row>
-    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>238</v>
       </c>
@@ -48010,7 +48011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -48087,7 +48088,7 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -48164,7 +48165,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -48241,7 +48242,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -48318,7 +48319,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -48395,7 +48396,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -48472,7 +48473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -48549,7 +48550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>240</v>
       </c>
@@ -48624,7 +48625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>251</v>
       </c>
@@ -48699,7 +48700,7 @@
       </c>
       <c r="Y623" s="3"/>
     </row>
-    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>254</v>
       </c>
@@ -48755,7 +48756,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>263</v>
       </c>
@@ -48832,7 +48833,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>265</v>
       </c>
@@ -48909,7 +48910,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>266</v>
       </c>
@@ -48986,7 +48987,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>300</v>
       </c>
@@ -49063,7 +49064,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>301</v>
       </c>
@@ -49140,7 +49141,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>306</v>
       </c>
@@ -49215,7 +49216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>306</v>
       </c>
@@ -49292,7 +49293,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -49369,7 +49370,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -49446,7 +49447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -49523,7 +49524,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -49600,7 +49601,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -49677,7 +49678,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>347</v>
       </c>
@@ -49754,7 +49755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>348</v>
       </c>
@@ -49831,7 +49832,7 @@
         <v>99.936143039591002</v>
       </c>
     </row>
-    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>351</v>
       </c>
@@ -49906,7 +49907,7 @@
         <v>11.41868512110727</v>
       </c>
     </row>
-    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>352</v>
       </c>
@@ -49981,7 +49982,7 @@
         <v>1.0385968556480199E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>368</v>
       </c>
@@ -50054,7 +50055,7 @@
       <c r="X641" s="3"/>
       <c r="Y641" s="3"/>
     </row>
-    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>372</v>
       </c>
@@ -50127,7 +50128,7 @@
       <c r="X642" s="3"/>
       <c r="Y642" s="3"/>
     </row>
-    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>373</v>
       </c>
@@ -50204,7 +50205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>373</v>
       </c>
@@ -50281,7 +50282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -50358,7 +50359,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -50435,7 +50436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -50512,7 +50513,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -50589,7 +50590,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -50666,7 +50667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>390</v>
       </c>
@@ -50743,7 +50744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>390</v>
       </c>
@@ -50820,7 +50821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -50897,7 +50898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -50974,7 +50975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -51051,7 +51052,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -51128,7 +51129,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -51205,7 +51206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -51282,7 +51283,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -51359,7 +51360,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -51436,7 +51437,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -51513,7 +51514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -51590,7 +51591,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -51667,7 +51668,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>394</v>
       </c>
@@ -51744,7 +51745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>395</v>
       </c>
@@ -51819,7 +51820,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>409</v>
       </c>
@@ -51890,7 +51891,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>409</v>
       </c>
@@ -51967,7 +51968,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -52044,7 +52045,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>414</v>
       </c>
@@ -52121,7 +52122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>414</v>
       </c>
@@ -52198,7 +52199,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -52275,7 +52276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -52352,7 +52353,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -52429,7 +52430,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -52506,7 +52507,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -52583,7 +52584,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -52660,7 +52661,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -52737,7 +52738,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -52814,7 +52815,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>415</v>
       </c>
@@ -52891,7 +52892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>415</v>
       </c>
@@ -52968,7 +52969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -53045,7 +53046,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -53122,7 +53123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -53199,7 +53200,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -53276,7 +53277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -53353,7 +53354,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -53430,7 +53431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -53507,7 +53508,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -53584,7 +53585,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -53661,7 +53662,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -53738,7 +53739,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -53815,7 +53816,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -53892,7 +53893,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -53969,7 +53970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>416</v>
       </c>
@@ -54046,7 +54047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>416</v>
       </c>
@@ -54123,7 +54124,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -54200,7 +54201,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -54277,7 +54278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -54354,7 +54355,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -54431,7 +54432,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -54508,7 +54509,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>417</v>
       </c>
@@ -54585,7 +54586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>417</v>
       </c>
@@ -54662,7 +54663,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -54739,7 +54740,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -54816,7 +54817,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -54893,7 +54894,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -54970,7 +54971,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -55047,7 +55048,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>418</v>
       </c>
@@ -55124,7 +55125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>418</v>
       </c>
@@ -55201,7 +55202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -55278,7 +55279,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -55355,7 +55356,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -55430,7 +55431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -55507,7 +55508,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -55584,7 +55585,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -55661,7 +55662,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -55738,7 +55739,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -55815,7 +55816,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>420</v>
       </c>
@@ -55892,7 +55893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>420</v>
       </c>
@@ -55969,7 +55970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -56046,7 +56047,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -56123,7 +56124,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -56200,7 +56201,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -56277,7 +56278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -56354,7 +56355,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>431</v>
       </c>
@@ -56427,7 +56428,7 @@
       <c r="X724" s="3"/>
       <c r="Y724" s="3"/>
     </row>
-    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>432</v>
       </c>
@@ -56504,7 +56505,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>432</v>
       </c>
@@ -56581,7 +56582,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -56658,7 +56659,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -56735,7 +56736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -56812,7 +56813,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -56889,7 +56890,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -56966,7 +56967,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -57043,7 +57044,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -57120,7 +57121,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -57197,7 +57198,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>453</v>
       </c>
@@ -57266,7 +57267,7 @@
       <c r="X735" s="3"/>
       <c r="Y735" s="3"/>
     </row>
-    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>455</v>
       </c>
@@ -57331,7 +57332,7 @@
       <c r="X736" s="3"/>
       <c r="Y736" s="3"/>
     </row>
-    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>456</v>
       </c>
@@ -57402,7 +57403,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>456</v>
       </c>
@@ -57479,7 +57480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -57556,7 +57557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -57633,7 +57634,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>457</v>
       </c>
@@ -57704,7 +57705,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>457</v>
       </c>
@@ -57781,7 +57782,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -57858,7 +57859,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -57935,7 +57936,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>469</v>
       </c>
@@ -58010,7 +58011,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>469</v>
       </c>
@@ -58087,7 +58088,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -58164,7 +58165,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -58241,7 +58242,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -58318,7 +58319,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -58395,7 +58396,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -58472,7 +58473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -58549,7 +58550,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -58626,7 +58627,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -58703,7 +58704,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -58780,7 +58781,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>470</v>
       </c>
@@ -58857,7 +58858,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>470</v>
       </c>
@@ -58932,7 +58933,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -59009,7 +59010,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -59086,7 +59087,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -59163,7 +59164,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -59240,7 +59241,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>471</v>
       </c>
@@ -59317,7 +59318,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>471</v>
       </c>
@@ -59394,7 +59395,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -59471,7 +59472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -59548,7 +59549,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -59625,7 +59626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -59702,7 +59703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -59779,7 +59780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -59856,7 +59857,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="770" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>484</v>
       </c>
@@ -59923,7 +59924,7 @@
       <c r="X770" s="3"/>
       <c r="Y770" s="3"/>
     </row>
-    <row r="771" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>510</v>
       </c>
@@ -59998,7 +59999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="772" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>510</v>
       </c>
@@ -60069,7 +60070,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="773" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>511</v>
       </c>
@@ -60144,7 +60145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="774" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>511</v>
       </c>
@@ -60221,7 +60222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -60298,7 +60299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="776" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -60375,7 +60376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="777" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -60452,7 +60453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="778" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -60529,7 +60530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="779" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -60606,7 +60607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="780" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -60683,7 +60684,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="781" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>513</v>
       </c>
@@ -60744,7 +60745,7 @@
       <c r="X781" s="3"/>
       <c r="Y781" s="3"/>
     </row>
-    <row r="782" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>518</v>
       </c>
@@ -60798,7 +60799,7 @@
       </c>
       <c r="R782" s="3"/>
     </row>
-    <row r="783" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>526</v>
       </c>
@@ -60855,7 +60856,7 @@
       <c r="X783" s="3"/>
       <c r="Y783" s="3"/>
     </row>
-    <row r="784" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>529</v>
       </c>
@@ -60930,7 +60931,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="785" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785">
         <v>529</v>
       </c>
@@ -61007,7 +61008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="786" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -61086,7 +61087,29 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}"/>
+  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Cantidad de usuarios - (Metrica)"/>
+        <filter val="Cartera - Metrica"/>
+        <filter val="Docentes contratados - Metrica"/>
+        <filter val="N de horas por solicitud - (Metrica)"/>
+        <filter val="N de horas promedio por evento - (Metrica)"/>
+        <filter val="N de personas promedio por evento - (Metrica)"/>
+        <filter val="N de solicitudes radicadas - (Metrica)"/>
+        <filter val="Número de estudiantes que ha realizado la simulación (Metrica)"/>
+        <filter val="Número de informes de autoevaluación con fines de acreditación en alta calidad radicados- Metrica"/>
+        <filter val="Número de programas con condiciones iniciales aprobadas (indicador externo)- Metrica"/>
+        <filter val="Número de programas con obtención de acreditación por primera vez- Metrica"/>
+        <filter val="Número de programas con renovación de acreditación en alta calidad - Metrica"/>
+        <filter val="Número de programas nuevos con registro calificado aprobado - Metrica"/>
+        <filter val="Portafolio de Proyectos - Metrica"/>
+        <filter val="Proyectos de investigación e innovación- Metrica"/>
+        <filter val="Tasa de cotización del graduado - Metrica"/>
+        <filter val="Total docentes por nivel de estudios - Metrica"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AB4F2B7-D6D9-4EFC-A9D7-9F152B215129}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33DF16E5-EB36-4DAD-A1FC-517F63C1983E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -3742,7 +3742,7 @@
       <sheetName val="Hoja3"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="A1" t="str">
@@ -6295,9 +6295,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6620,6 +6620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6704,7 +6705,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -6774,7 +6775,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -6844,7 +6845,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -6914,7 +6915,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -6984,7 +6985,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -7054,7 +7055,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -7124,7 +7125,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -7194,7 +7195,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -7264,7 +7265,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -7334,7 +7335,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -7404,7 +7405,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -7474,7 +7475,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -7544,7 +7545,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -7611,7 +7612,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -7680,7 +7681,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -7749,7 +7750,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -7818,7 +7819,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -7887,7 +7888,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -7948,7 +7949,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -8017,7 +8018,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -8086,7 +8087,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -8156,7 +8157,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -8226,7 +8227,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -8293,7 +8294,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -8357,7 +8358,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -8417,7 +8418,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -8480,7 +8481,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -8545,7 +8546,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -8607,7 +8608,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -8665,7 +8666,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -8723,7 +8724,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -8797,7 +8798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -8871,7 +8872,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -8945,7 +8946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -9019,7 +9020,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -9093,7 +9094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -9167,7 +9168,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -9241,7 +9242,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>221</v>
       </c>
@@ -9305,7 +9306,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -9379,7 +9380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -9453,7 +9454,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -9527,7 +9528,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -9601,7 +9602,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -9675,7 +9676,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -9749,7 +9750,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>222</v>
       </c>
@@ -9823,7 +9824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -9897,7 +9898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -9969,7 +9970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -10043,7 +10044,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -10117,7 +10118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -10177,7 +10178,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -10251,7 +10252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -10325,7 +10326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -10399,7 +10400,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -10471,7 +10472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -10545,7 +10546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -10619,7 +10620,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -10691,7 +10692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -10765,7 +10766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -10839,7 +10840,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -10913,7 +10914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -10987,7 +10988,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -11061,7 +11062,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -11135,7 +11136,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -11207,7 +11208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -11281,7 +11282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -11351,7 +11352,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -11425,7 +11426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -11495,7 +11496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -11565,7 +11566,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -11639,7 +11640,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -11711,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -11785,7 +11786,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -11859,7 +11860,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -11933,7 +11934,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -12007,7 +12008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -12081,7 +12082,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -12155,7 +12156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -12212,7 +12213,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -12268,7 +12269,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -12336,7 +12337,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -12398,7 +12399,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -12472,7 +12473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -12546,7 +12547,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -12620,7 +12621,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -12694,7 +12695,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -12768,7 +12769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -12842,7 +12843,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -12904,7 +12905,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -12963,7 +12964,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -13021,7 +13022,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>326</v>
       </c>
@@ -13079,7 +13080,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -13139,7 +13140,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -13195,7 +13196,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -13253,7 +13254,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -13311,7 +13312,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -13367,7 +13368,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -13425,7 +13426,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -13483,7 +13484,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>367</v>
       </c>
@@ -13541,7 +13542,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -13599,7 +13600,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -13657,7 +13658,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -13713,7 +13714,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -13769,7 +13770,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -13825,7 +13826,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -13883,7 +13884,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -13941,7 +13942,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -13999,7 +14000,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -14055,7 +14056,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -14111,7 +14112,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -14223,7 +14224,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -14279,7 +14280,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -14335,7 +14336,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -14391,7 +14392,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>495</v>
       </c>
@@ -14447,7 +14448,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -14503,7 +14504,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>498</v>
       </c>
@@ -14559,7 +14560,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>499</v>
       </c>
@@ -14613,7 +14614,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>500</v>
       </c>
@@ -14669,7 +14670,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>501</v>
       </c>
@@ -14725,7 +14726,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>502</v>
       </c>
@@ -14781,7 +14782,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>503</v>
       </c>
@@ -14837,7 +14838,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>504</v>
       </c>
@@ -14893,7 +14894,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>505</v>
       </c>
@@ -14949,7 +14950,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>508</v>
       </c>
@@ -15005,7 +15006,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>522</v>
       </c>
@@ -15059,7 +15060,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>527</v>
       </c>
@@ -15111,7 +15112,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>528</v>
       </c>
@@ -15166,7 +15167,7 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>541</v>
       </c>
@@ -15220,7 +15221,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>542</v>
       </c>
@@ -15284,7 +15285,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>542</v>
       </c>
@@ -15358,7 +15359,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>542</v>
       </c>
@@ -15432,7 +15433,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>542</v>
       </c>
@@ -15506,7 +15507,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>542</v>
       </c>
@@ -15580,7 +15581,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>546</v>
       </c>
@@ -15642,7 +15643,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>546</v>
       </c>
@@ -15713,7 +15714,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -15784,7 +15785,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -15855,7 +15856,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>547</v>
       </c>
@@ -15909,7 +15910,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>552</v>
       </c>
@@ -15963,7 +15964,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>553</v>
       </c>
@@ -16017,7 +16018,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>556</v>
       </c>
@@ -16071,7 +16072,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>290</v>
       </c>
@@ -16144,7 +16145,7 @@
         <v>91.666666666666657</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>290</v>
       </c>
@@ -16218,7 +16219,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -16292,7 +16293,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -16366,7 +16367,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -16440,7 +16441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -16514,7 +16515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -16588,7 +16589,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -16662,7 +16663,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -16736,7 +16737,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -16810,7 +16811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>77</v>
       </c>
@@ -16887,7 +16888,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>121</v>
       </c>
@@ -16964,7 +16965,7 @@
         <v>99.18</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>122</v>
       </c>
@@ -17041,7 +17042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>124</v>
       </c>
@@ -17118,7 +17119,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>125</v>
       </c>
@@ -17195,7 +17196,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>128</v>
       </c>
@@ -17272,7 +17273,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>172</v>
       </c>
@@ -17349,7 +17350,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>208</v>
       </c>
@@ -17426,7 +17427,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>208</v>
       </c>
@@ -17503,7 +17504,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -17580,7 +17581,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -17657,7 +17658,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -17734,7 +17735,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -17811,7 +17812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -17888,7 +17889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>214</v>
       </c>
@@ -17965,7 +17966,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>214</v>
       </c>
@@ -18042,7 +18043,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -18119,7 +18120,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -18196,7 +18197,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -18273,7 +18274,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -18350,7 +18351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -18427,7 +18428,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>217</v>
       </c>
@@ -18504,7 +18505,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>217</v>
       </c>
@@ -18581,7 +18582,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -18658,7 +18659,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -18735,7 +18736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -18812,7 +18813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -18889,7 +18890,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -18966,7 +18967,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>218</v>
       </c>
@@ -19043,7 +19044,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>218</v>
       </c>
@@ -19120,7 +19121,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -19197,7 +19198,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -19274,7 +19275,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -19351,7 +19352,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -19428,7 +19429,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -19505,7 +19506,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>225</v>
       </c>
@@ -19580,7 +19581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>225</v>
       </c>
@@ -19657,7 +19658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -19732,7 +19733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -19809,7 +19810,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -19886,7 +19887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -19963,7 +19964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -20569,7 +20570,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>434</v>
       </c>
@@ -20644,7 +20645,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>434</v>
       </c>
@@ -20721,7 +20722,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -20798,7 +20799,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -20875,7 +20876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -20952,7 +20953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -21029,7 +21030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -21106,7 +21107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>436</v>
       </c>
@@ -21183,7 +21184,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>436</v>
       </c>
@@ -21260,7 +21261,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -21337,7 +21338,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>485</v>
       </c>
@@ -21410,7 +21411,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>485</v>
       </c>
@@ -21482,7 +21483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -21556,7 +21557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -21630,7 +21631,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -21704,7 +21705,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -21778,7 +21779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -21852,7 +21853,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -21926,7 +21927,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -22000,7 +22001,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -22074,7 +22075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>488</v>
       </c>
@@ -22149,7 +22150,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>488</v>
       </c>
@@ -22223,7 +22224,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -22297,7 +22298,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -22371,7 +22372,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -22445,7 +22446,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -22519,7 +22520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -22593,7 +22594,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -22667,7 +22668,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -22741,7 +22742,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -24208,7 +24209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>68</v>
       </c>
@@ -24283,7 +24284,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>73</v>
       </c>
@@ -24360,7 +24361,7 @@
         <v>18.41</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>74</v>
       </c>
@@ -24437,7 +24438,7 @@
         <v>80.327868852459019</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>86</v>
       </c>
@@ -24514,7 +24515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>95</v>
       </c>
@@ -24591,7 +24592,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>143</v>
       </c>
@@ -24668,7 +24669,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>145</v>
       </c>
@@ -24745,7 +24746,7 @@
         <v>1.545454545454545</v>
       </c>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>146</v>
       </c>
@@ -24822,7 +24823,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>148</v>
       </c>
@@ -24899,7 +24900,7 @@
         <v>1.977873977873978</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>159</v>
       </c>
@@ -24949,7 +24950,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>167</v>
       </c>
@@ -25020,7 +25021,7 @@
       <c r="X262" s="3"/>
       <c r="Y262" s="3"/>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>193</v>
       </c>
@@ -25085,7 +25086,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>199</v>
       </c>
@@ -25154,7 +25155,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>203</v>
       </c>
@@ -25231,7 +25232,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>203</v>
       </c>
@@ -25308,7 +25309,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -25385,7 +25386,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -25462,7 +25463,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>204</v>
       </c>
@@ -25527,7 +25528,7 @@
       <c r="X269" s="3"/>
       <c r="Y269" s="3"/>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>205</v>
       </c>
@@ -25592,7 +25593,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>207</v>
       </c>
@@ -25657,7 +25658,7 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>215</v>
       </c>
@@ -25734,7 +25735,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>215</v>
       </c>
@@ -25811,7 +25812,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -25888,7 +25889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -25965,7 +25966,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -26042,7 +26043,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -26119,7 +26120,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -26196,7 +26197,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>219</v>
       </c>
@@ -26271,7 +26272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>219</v>
       </c>
@@ -26348,7 +26349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -26425,7 +26426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -26502,7 +26503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -26579,7 +26580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -26656,7 +26657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -26733,7 +26734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -26791,7 +26792,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>220</v>
       </c>
@@ -26866,7 +26867,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>220</v>
       </c>
@@ -26943,7 +26944,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -27020,7 +27021,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -27097,7 +27098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -27174,7 +27175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -27247,7 +27248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -27324,7 +27325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>230</v>
       </c>
@@ -27387,7 +27388,7 @@
       <c r="X294" s="3"/>
       <c r="Y294" s="3"/>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>231</v>
       </c>
@@ -27450,7 +27451,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>232</v>
       </c>
@@ -27513,7 +27514,7 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>245</v>
       </c>
@@ -27578,7 +27579,7 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>246</v>
       </c>
@@ -27641,7 +27642,7 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>252</v>
       </c>
@@ -27706,7 +27707,7 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>256</v>
       </c>
@@ -27769,7 +27770,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>260</v>
       </c>
@@ -27834,7 +27835,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>261</v>
       </c>
@@ -27899,7 +27900,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>262</v>
       </c>
@@ -27962,7 +27963,7 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
     </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>268</v>
       </c>
@@ -28027,7 +28028,7 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>269</v>
       </c>
@@ -28092,7 +28093,7 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
     </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>270</v>
       </c>
@@ -28157,7 +28158,7 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>271</v>
       </c>
@@ -28222,7 +28223,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>273</v>
       </c>
@@ -28287,7 +28288,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>274</v>
       </c>
@@ -28364,7 +28365,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>274</v>
       </c>
@@ -28441,7 +28442,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -28518,7 +28519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -28595,7 +28596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -28672,7 +28673,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>275</v>
       </c>
@@ -28749,7 +28750,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>275</v>
       </c>
@@ -28826,7 +28827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -28903,7 +28904,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -28980,7 +28981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>276</v>
       </c>
@@ -29045,7 +29046,7 @@
       <c r="X318" s="3"/>
       <c r="Y318" s="3"/>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>277</v>
       </c>
@@ -29110,7 +29111,7 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
     </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>278</v>
       </c>
@@ -29187,7 +29188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>278</v>
       </c>
@@ -29264,7 +29265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>278</v>
       </c>
@@ -29341,7 +29342,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>278</v>
       </c>
@@ -29418,7 +29419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>282</v>
       </c>
@@ -29483,7 +29484,7 @@
       <c r="X324" s="3"/>
       <c r="Y324" s="3"/>
     </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>283</v>
       </c>
@@ -29548,7 +29549,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>285</v>
       </c>
@@ -29613,7 +29614,7 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
     </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>286</v>
       </c>
@@ -29690,7 +29691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>286</v>
       </c>
@@ -29767,7 +29768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>286</v>
       </c>
@@ -29844,7 +29845,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>286</v>
       </c>
@@ -29921,7 +29922,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>286</v>
       </c>
@@ -29998,7 +29999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>292</v>
       </c>
@@ -30075,7 +30076,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>292</v>
       </c>
@@ -30152,7 +30153,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -30229,7 +30230,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -30306,7 +30307,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>294</v>
       </c>
@@ -30383,7 +30384,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>294</v>
       </c>
@@ -30460,7 +30461,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -30537,7 +30538,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -30614,7 +30615,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>302</v>
       </c>
@@ -30691,7 +30692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>302</v>
       </c>
@@ -30768,7 +30769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>302</v>
       </c>
@@ -30845,7 +30846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>302</v>
       </c>
@@ -30922,7 +30923,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>302</v>
       </c>
@@ -30999,7 +31000,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>303</v>
       </c>
@@ -31074,7 +31075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>303</v>
       </c>
@@ -31151,7 +31152,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -31228,7 +31229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -31305,7 +31306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>304</v>
       </c>
@@ -31370,7 +31371,7 @@
       <c r="X349" s="3"/>
       <c r="Y349" s="3"/>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>323</v>
       </c>
@@ -31435,7 +31436,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>324</v>
       </c>
@@ -31500,7 +31501,7 @@
       <c r="X351" s="3"/>
       <c r="Y351" s="3"/>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>325</v>
       </c>
@@ -31565,7 +31566,7 @@
       <c r="X352" s="3"/>
       <c r="Y352" s="3"/>
     </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>327</v>
       </c>
@@ -31630,7 +31631,7 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>332</v>
       </c>
@@ -31695,7 +31696,7 @@
       <c r="X354" s="3"/>
       <c r="Y354" s="3"/>
     </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>337</v>
       </c>
@@ -31760,7 +31761,7 @@
       <c r="X355" s="3"/>
       <c r="Y355" s="3"/>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>338</v>
       </c>
@@ -31825,7 +31826,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>341</v>
       </c>
@@ -31890,7 +31891,7 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>344</v>
       </c>
@@ -31955,7 +31956,7 @@
       <c r="X358" s="3"/>
       <c r="Y358" s="3"/>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>356</v>
       </c>
@@ -32020,7 +32021,7 @@
       <c r="X359" s="3"/>
       <c r="Y359" s="3"/>
     </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>357</v>
       </c>
@@ -32081,7 +32082,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>358</v>
       </c>
@@ -32146,7 +32147,7 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>359</v>
       </c>
@@ -32207,7 +32208,7 @@
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -32284,7 +32285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>362</v>
       </c>
@@ -32361,7 +32362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -32438,7 +32439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>363</v>
       </c>
@@ -32501,7 +32502,7 @@
       <c r="X366" s="3"/>
       <c r="Y366" s="3"/>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>364</v>
       </c>
@@ -32566,7 +32567,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>369</v>
       </c>
@@ -32643,7 +32644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>369</v>
       </c>
@@ -32720,7 +32721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -32797,7 +32798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>371</v>
       </c>
@@ -32862,7 +32863,7 @@
       <c r="X371" s="3"/>
       <c r="Y371" s="3"/>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>375</v>
       </c>
@@ -32939,7 +32940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -33016,7 +33017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -33093,7 +33094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>376</v>
       </c>
@@ -33158,7 +33159,7 @@
       <c r="X375" s="3"/>
       <c r="Y375" s="3"/>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>379</v>
       </c>
@@ -33223,7 +33224,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>381</v>
       </c>
@@ -33288,7 +33289,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>382</v>
       </c>
@@ -33353,7 +33354,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>383</v>
       </c>
@@ -33418,7 +33419,7 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>384</v>
       </c>
@@ -33483,7 +33484,7 @@
       <c r="X380" s="3"/>
       <c r="Y380" s="3"/>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>385</v>
       </c>
@@ -33548,7 +33549,7 @@
       <c r="X381" s="3"/>
       <c r="Y381" s="3"/>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>386</v>
       </c>
@@ -33625,7 +33626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>386</v>
       </c>
@@ -33702,7 +33703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -33779,7 +33780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -33856,7 +33857,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>389</v>
       </c>
@@ -33929,7 +33930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -34003,7 +34004,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -34077,7 +34078,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -34151,7 +34152,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -34225,7 +34226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -34299,7 +34300,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -34373,7 +34374,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -34447,7 +34448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -34521,7 +34522,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -34595,7 +34596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -34669,7 +34670,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -34743,7 +34744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -34817,7 +34818,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -34882,7 +34883,7 @@
       <c r="X399" s="3"/>
       <c r="Y399" s="3"/>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -34947,7 +34948,7 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -35012,7 +35013,7 @@
       <c r="X401" s="3"/>
       <c r="Y401" s="3"/>
     </row>
-    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -35077,7 +35078,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -35142,7 +35143,7 @@
       <c r="X403" s="3"/>
       <c r="Y403" s="3"/>
     </row>
-    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -35207,7 +35208,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>408</v>
       </c>
@@ -35284,7 +35285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -35361,7 +35362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -35438,7 +35439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -35515,7 +35516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>422</v>
       </c>
@@ -35580,7 +35581,7 @@
       <c r="X409" s="3"/>
       <c r="Y409" s="3"/>
     </row>
-    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>426</v>
       </c>
@@ -35639,7 +35640,7 @@
       <c r="X410" s="3"/>
       <c r="Y410" s="3"/>
     </row>
-    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>427</v>
       </c>
@@ -35716,7 +35717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>427</v>
       </c>
@@ -35793,7 +35794,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -35870,7 +35871,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -35947,7 +35948,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -36024,7 +36025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -36097,7 +36098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -36174,7 +36175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>428</v>
       </c>
@@ -36251,7 +36252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>428</v>
       </c>
@@ -36328,7 +36329,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -36405,7 +36406,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -36480,7 +36481,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -36557,7 +36558,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -36630,7 +36631,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -36705,7 +36706,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -36759,7 +36760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>429</v>
       </c>
@@ -36836,7 +36837,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -36913,7 +36914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -36990,7 +36991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -37067,7 +37068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -37144,7 +37145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -37221,7 +37222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -37298,7 +37299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>430</v>
       </c>
@@ -37375,7 +37376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>430</v>
       </c>
@@ -37452,7 +37453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -37529,7 +37530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -37606,7 +37607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -37683,7 +37684,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>433</v>
       </c>
@@ -37760,7 +37761,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>433</v>
       </c>
@@ -37837,7 +37838,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -37914,7 +37915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -37991,7 +37992,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -38064,7 +38065,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -38135,7 +38136,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -38210,7 +38211,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -38268,7 +38269,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>435</v>
       </c>
@@ -38343,7 +38344,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>435</v>
       </c>
@@ -38420,7 +38421,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -38497,7 +38498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -38574,7 +38575,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -38651,7 +38652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -38728,7 +38729,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -38805,7 +38806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>439</v>
       </c>
@@ -38882,7 +38883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>439</v>
       </c>
@@ -38959,7 +38960,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -39036,7 +39037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>440</v>
       </c>
@@ -39113,7 +39114,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>440</v>
       </c>
@@ -39190,7 +39191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -39267,7 +39268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>444</v>
       </c>
@@ -39326,7 +39327,7 @@
       <c r="X459" s="3"/>
       <c r="Y459" s="3"/>
     </row>
-    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>445</v>
       </c>
@@ -39387,7 +39388,7 @@
       <c r="X460" s="3"/>
       <c r="Y460" s="3"/>
     </row>
-    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>447</v>
       </c>
@@ -39448,7 +39449,7 @@
       <c r="X461" s="3"/>
       <c r="Y461" s="3"/>
     </row>
-    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>448</v>
       </c>
@@ -39509,7 +39510,7 @@
       <c r="X462" s="3"/>
       <c r="Y462" s="3"/>
     </row>
-    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>451</v>
       </c>
@@ -39570,7 +39571,7 @@
       <c r="X463" s="3"/>
       <c r="Y463" s="3"/>
     </row>
-    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>452</v>
       </c>
@@ -39627,7 +39628,7 @@
       <c r="X464" s="3"/>
       <c r="Y464" s="3"/>
     </row>
-    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>466</v>
       </c>
@@ -39688,7 +39689,7 @@
       <c r="X465" s="3"/>
       <c r="Y465" s="3"/>
     </row>
-    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>467</v>
       </c>
@@ -39749,7 +39750,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
     </row>
-    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>468</v>
       </c>
@@ -39810,7 +39811,7 @@
       <c r="X467" s="3"/>
       <c r="Y467" s="3"/>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>473</v>
       </c>
@@ -39887,7 +39888,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -39964,7 +39965,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>473</v>
       </c>
@@ -40041,7 +40042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>473</v>
       </c>
@@ -40118,7 +40119,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>474</v>
       </c>
@@ -40191,7 +40192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>474</v>
       </c>
@@ -40265,7 +40266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -40339,7 +40340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -40413,7 +40414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -40487,7 +40488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -40561,7 +40562,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -40635,7 +40636,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -40709,7 +40710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -40783,7 +40784,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -40857,7 +40858,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -40931,7 +40932,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -41005,7 +41006,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -41079,7 +41080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>475</v>
       </c>
@@ -41140,7 +41141,7 @@
       <c r="X485" s="3"/>
       <c r="Y485" s="3"/>
     </row>
-    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>476</v>
       </c>
@@ -41217,7 +41218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>476</v>
       </c>
@@ -41294,7 +41295,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -41371,7 +41372,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -41448,7 +41449,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>477</v>
       </c>
@@ -41519,7 +41520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>477</v>
       </c>
@@ -41593,7 +41594,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -41667,7 +41668,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -41741,7 +41742,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -41815,7 +41816,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -41889,7 +41890,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -41963,7 +41964,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -42037,7 +42038,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -42111,7 +42112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -42185,7 +42186,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -42259,7 +42260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -42333,7 +42334,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -42407,7 +42408,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>478</v>
       </c>
@@ -42480,7 +42481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>478</v>
       </c>
@@ -42554,7 +42555,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -42628,7 +42629,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -42702,7 +42703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -42776,7 +42777,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -42850,7 +42851,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -42924,7 +42925,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -42998,7 +42999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -43072,7 +43073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -43146,7 +43147,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -43220,7 +43221,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -43294,7 +43295,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -43368,7 +43369,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>479</v>
       </c>
@@ -43441,7 +43442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>479</v>
       </c>
@@ -43518,7 +43519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -43595,7 +43596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -43672,7 +43673,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -43749,7 +43750,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -43826,7 +43827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -43903,7 +43904,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -43980,7 +43981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -44057,7 +44058,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -44134,7 +44135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -44211,7 +44212,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -44288,7 +44289,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -44365,7 +44366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>480</v>
       </c>
@@ -44438,7 +44439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>480</v>
       </c>
@@ -44515,7 +44516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -44592,7 +44593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -44669,7 +44670,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -44746,7 +44747,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -44823,7 +44824,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -44900,7 +44901,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -44977,7 +44978,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -45054,7 +45055,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -45131,7 +45132,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -45208,7 +45209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -45285,7 +45286,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -45362,7 +45363,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>481</v>
       </c>
@@ -45423,7 +45424,7 @@
       <c r="X542" s="3"/>
       <c r="Y542" s="3"/>
     </row>
-    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>481</v>
       </c>
@@ -45493,7 +45494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>486</v>
       </c>
@@ -45552,7 +45553,7 @@
       <c r="X544" s="3"/>
       <c r="Y544" s="3"/>
     </row>
-    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>506</v>
       </c>
@@ -45611,7 +45612,7 @@
       <c r="X545" s="3"/>
       <c r="Y545" s="3"/>
     </row>
-    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>507</v>
       </c>
@@ -45670,7 +45671,7 @@
       <c r="X546" s="3"/>
       <c r="Y546" s="3"/>
     </row>
-    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>514</v>
       </c>
@@ -45727,7 +45728,7 @@
       <c r="X547" s="3"/>
       <c r="Y547" s="3"/>
     </row>
-    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>515</v>
       </c>
@@ -45782,7 +45783,7 @@
       <c r="X548" s="3"/>
       <c r="Y548" s="3"/>
     </row>
-    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>516</v>
       </c>
@@ -45837,7 +45838,7 @@
       <c r="X549" s="3"/>
       <c r="Y549" s="3"/>
     </row>
-    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>519</v>
       </c>
@@ -45914,7 +45915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>519</v>
       </c>
@@ -45991,7 +45992,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -46068,7 +46069,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>523</v>
       </c>
@@ -46145,7 +46146,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>523</v>
       </c>
@@ -46222,7 +46223,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -46299,7 +46300,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -46376,7 +46377,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>524</v>
       </c>
@@ -46453,7 +46454,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>524</v>
       </c>
@@ -46530,7 +46531,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -46607,7 +46608,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="560" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -46684,7 +46685,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -46761,7 +46762,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -46838,7 +46839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="563" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -46915,7 +46916,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>530</v>
       </c>
@@ -46970,7 +46971,7 @@
       <c r="X564" s="3"/>
       <c r="Y564" s="3"/>
     </row>
-    <row r="565" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>531</v>
       </c>
@@ -47025,7 +47026,7 @@
       <c r="X565" s="3"/>
       <c r="Y565" s="3"/>
     </row>
-    <row r="566" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>532</v>
       </c>
@@ -47094,7 +47095,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>532</v>
       </c>
@@ -47171,7 +47172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -47248,7 +47249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -47325,7 +47326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -47402,7 +47403,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>533</v>
       </c>
@@ -47479,7 +47480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>533</v>
       </c>
@@ -47556,7 +47557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -47633,7 +47634,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>534</v>
       </c>
@@ -47710,7 +47711,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>534</v>
       </c>
@@ -47787,7 +47788,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -47864,7 +47865,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>535</v>
       </c>
@@ -47941,7 +47942,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -48018,7 +48019,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -48095,7 +48096,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>536</v>
       </c>
@@ -48172,7 +48173,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>536</v>
       </c>
@@ -48249,7 +48250,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -48326,7 +48327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>537</v>
       </c>
@@ -48383,7 +48384,7 @@
       <c r="X583" s="3"/>
       <c r="Y583" s="3"/>
     </row>
-    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>538</v>
       </c>
@@ -48438,7 +48439,7 @@
       <c r="X584" s="3"/>
       <c r="Y584" s="3"/>
     </row>
-    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>539</v>
       </c>
@@ -48493,7 +48494,7 @@
       <c r="X585" s="3"/>
       <c r="Y585" s="3"/>
     </row>
-    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>540</v>
       </c>
@@ -48550,7 +48551,7 @@
       <c r="X586" s="3"/>
       <c r="Y586" s="3"/>
     </row>
-    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>543</v>
       </c>
@@ -48625,7 +48626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>543</v>
       </c>
@@ -48702,7 +48703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -48779,7 +48780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>544</v>
       </c>
@@ -48854,7 +48855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>544</v>
       </c>
@@ -48931,7 +48932,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -49008,7 +49009,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -49085,7 +49086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -49162,7 +49163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>550</v>
       </c>
@@ -49219,7 +49220,7 @@
       <c r="X595" s="3"/>
       <c r="Y595" s="3"/>
     </row>
-    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>551</v>
       </c>
@@ -49276,7 +49277,7 @@
       <c r="X596" s="3"/>
       <c r="Y596" s="3"/>
     </row>
-    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>554</v>
       </c>
@@ -49331,7 +49332,7 @@
       <c r="X597" s="3"/>
       <c r="Y597" s="3"/>
     </row>
-    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>555</v>
       </c>
@@ -49386,7 +49387,7 @@
       <c r="X598" s="3"/>
       <c r="Y598" s="3"/>
     </row>
-    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>69</v>
       </c>
@@ -49463,7 +49464,7 @@
         <v>90.541781450871994</v>
       </c>
     </row>
-    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>111</v>
       </c>
@@ -49540,7 +49541,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>197</v>
       </c>
@@ -49617,7 +49618,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>213</v>
       </c>
@@ -49694,7 +49695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>213</v>
       </c>
@@ -49771,7 +49772,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -49848,7 +49849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -49925,7 +49926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -50002,7 +50003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -50079,7 +50080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -50156,7 +50157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -50233,7 +50234,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -50310,7 +50311,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>233</v>
       </c>
@@ -50385,7 +50386,7 @@
         <v>64.367816091954026</v>
       </c>
     </row>
-    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>234</v>
       </c>
@@ -50460,7 +50461,7 @@
         <v>3692.25</v>
       </c>
     </row>
-    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>238</v>
       </c>
@@ -50533,7 +50534,7 @@
         <v>94.444444444444443</v>
       </c>
     </row>
-    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>238</v>
       </c>
@@ -50610,7 +50611,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -50687,7 +50688,7 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -50764,7 +50765,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -50841,7 +50842,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -50918,7 +50919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -50995,7 +50996,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -51072,7 +51073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -51224,7 +51225,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>251</v>
       </c>
@@ -51299,7 +51300,7 @@
       </c>
       <c r="Y623" s="3"/>
     </row>
-    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>254</v>
       </c>
@@ -51355,7 +51356,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>263</v>
       </c>
@@ -51432,7 +51433,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>265</v>
       </c>
@@ -51509,7 +51510,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>266</v>
       </c>
@@ -51586,7 +51587,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>300</v>
       </c>
@@ -51663,7 +51664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>301</v>
       </c>
@@ -51740,7 +51741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>306</v>
       </c>
@@ -51815,7 +51816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>306</v>
       </c>
@@ -51892,7 +51893,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -51969,7 +51970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -52046,7 +52047,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -52123,7 +52124,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -52200,7 +52201,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -52277,7 +52278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>347</v>
       </c>
@@ -52354,7 +52355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>348</v>
       </c>
@@ -52431,7 +52432,7 @@
         <v>99.936143039591002</v>
       </c>
     </row>
-    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>351</v>
       </c>
@@ -52506,7 +52507,7 @@
         <v>11.41868512110727</v>
       </c>
     </row>
-    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>352</v>
       </c>
@@ -52581,7 +52582,7 @@
         <v>1.0385968556480199E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>368</v>
       </c>
@@ -52654,7 +52655,7 @@
       <c r="X641" s="3"/>
       <c r="Y641" s="3"/>
     </row>
-    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>372</v>
       </c>
@@ -52727,7 +52728,7 @@
       <c r="X642" s="3"/>
       <c r="Y642" s="3"/>
     </row>
-    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>373</v>
       </c>
@@ -52804,7 +52805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>373</v>
       </c>
@@ -52881,7 +52882,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -52958,7 +52959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -53035,7 +53036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -53112,7 +53113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -53189,7 +53190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -53266,7 +53267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>390</v>
       </c>
@@ -53343,7 +53344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>390</v>
       </c>
@@ -53420,7 +53421,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -53497,7 +53498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -53574,7 +53575,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -53651,7 +53652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -53728,7 +53729,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -53805,7 +53806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -53882,7 +53883,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -53959,7 +53960,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -54036,7 +54037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -54113,7 +54114,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -54190,7 +54191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -54267,7 +54268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>394</v>
       </c>
@@ -54344,7 +54345,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>395</v>
       </c>
@@ -54419,7 +54420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>409</v>
       </c>
@@ -54490,7 +54491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>409</v>
       </c>
@@ -54567,7 +54568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -54644,7 +54645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>414</v>
       </c>
@@ -54721,7 +54722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>414</v>
       </c>
@@ -54798,7 +54799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -54875,7 +54876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -54952,7 +54953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -55029,7 +55030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -55106,7 +55107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -55183,7 +55184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -55260,7 +55261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -55337,7 +55338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -55414,7 +55415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>415</v>
       </c>
@@ -55491,7 +55492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>415</v>
       </c>
@@ -55568,7 +55569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -55645,7 +55646,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -55722,7 +55723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -55799,7 +55800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -55876,7 +55877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -55953,7 +55954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -56030,7 +56031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -56107,7 +56108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -56184,7 +56185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -56261,7 +56262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -56338,7 +56339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -56415,7 +56416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -56492,7 +56493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -56569,7 +56570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>416</v>
       </c>
@@ -56646,7 +56647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>416</v>
       </c>
@@ -56723,7 +56724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -56800,7 +56801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -56877,7 +56878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -56954,7 +56955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -57031,7 +57032,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -57108,7 +57109,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>417</v>
       </c>
@@ -57185,7 +57186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>417</v>
       </c>
@@ -57262,7 +57263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -57339,7 +57340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -57416,7 +57417,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -57493,7 +57494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -57570,7 +57571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -57647,7 +57648,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>418</v>
       </c>
@@ -57724,7 +57725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>418</v>
       </c>
@@ -57801,7 +57802,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -57878,7 +57879,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -57955,7 +57956,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -58030,7 +58031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -58107,7 +58108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -58184,7 +58185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -58261,7 +58262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -58338,7 +58339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -58415,7 +58416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>420</v>
       </c>
@@ -58492,7 +58493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>420</v>
       </c>
@@ -58569,7 +58570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -58646,7 +58647,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -58723,7 +58724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -58800,7 +58801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -58877,7 +58878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -58954,7 +58955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>431</v>
       </c>
@@ -59027,7 +59028,7 @@
       <c r="X724" s="3"/>
       <c r="Y724" s="3"/>
     </row>
-    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>432</v>
       </c>
@@ -59104,7 +59105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>432</v>
       </c>
@@ -59181,7 +59182,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -59258,7 +59259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -59335,7 +59336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -59412,7 +59413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -59489,7 +59490,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -59566,7 +59567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -59643,7 +59644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -59720,7 +59721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -59797,7 +59798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>453</v>
       </c>
@@ -59866,7 +59867,7 @@
       <c r="X735" s="3"/>
       <c r="Y735" s="3"/>
     </row>
-    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>455</v>
       </c>
@@ -59931,7 +59932,7 @@
       <c r="X736" s="3"/>
       <c r="Y736" s="3"/>
     </row>
-    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>456</v>
       </c>
@@ -60002,7 +60003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>456</v>
       </c>
@@ -60079,7 +60080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -60156,7 +60157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -60233,7 +60234,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>457</v>
       </c>
@@ -60304,7 +60305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>457</v>
       </c>
@@ -60381,7 +60382,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -60458,7 +60459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -60535,7 +60536,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>469</v>
       </c>
@@ -60610,7 +60611,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>469</v>
       </c>
@@ -60687,7 +60688,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -60764,7 +60765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -60841,7 +60842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -60918,7 +60919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -60995,7 +60996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -61072,7 +61073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -61149,7 +61150,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -61226,7 +61227,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -61303,7 +61304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -61380,7 +61381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>470</v>
       </c>
@@ -61457,7 +61458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>470</v>
       </c>
@@ -61532,7 +61533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -61609,7 +61610,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -61686,7 +61687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -61763,7 +61764,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -61840,7 +61841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>471</v>
       </c>
@@ -61917,7 +61918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>471</v>
       </c>
@@ -61994,7 +61995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -62071,7 +62072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -62148,7 +62149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -62225,7 +62226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -62302,7 +62303,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -62379,7 +62380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -62456,7 +62457,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="770" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>484</v>
       </c>
@@ -62523,7 +62524,7 @@
       <c r="X770" s="3"/>
       <c r="Y770" s="3"/>
     </row>
-    <row r="771" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>510</v>
       </c>
@@ -62598,7 +62599,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="772" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>510</v>
       </c>
@@ -62669,7 +62670,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="773" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>511</v>
       </c>
@@ -62744,7 +62745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="774" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>511</v>
       </c>
@@ -62821,7 +62822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -62898,7 +62899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="776" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -62975,7 +62976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="777" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -63052,7 +63053,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="778" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -63129,7 +63130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="779" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -63206,7 +63207,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="780" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -63283,7 +63284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="781" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>513</v>
       </c>
@@ -63344,7 +63345,7 @@
       <c r="X781" s="3"/>
       <c r="Y781" s="3"/>
     </row>
-    <row r="782" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>518</v>
       </c>
@@ -63398,7 +63399,7 @@
       </c>
       <c r="R782" s="3"/>
     </row>
-    <row r="783" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>526</v>
       </c>
@@ -63455,7 +63456,7 @@
       <c r="X783" s="3"/>
       <c r="Y783" s="3"/>
     </row>
-    <row r="784" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>529</v>
       </c>
@@ -63530,7 +63531,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="785" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785">
         <v>529</v>
       </c>
@@ -63607,7 +63608,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="786" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -63686,7 +63687,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}"/>
+  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Gestión de Proyectos"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33DF16E5-EB36-4DAD-A1FC-517F63C1983E}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D522549C-79D0-4771-970F-C66CD7E8BE93}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -3735,15 +3735,14 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Hoja4"/>
       <sheetName val="Worksheet"/>
       <sheetName val="Hoja2"/>
+      <sheetName val="Hoja4"/>
       <sheetName val="Hoja1"/>
       <sheetName val="Hoja3"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
             <v>Id</v>
@@ -6295,9 +6294,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6620,7 +6620,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6705,7 +6704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -6775,7 +6774,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -6845,7 +6844,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -6915,7 +6914,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -6985,7 +6984,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -7055,7 +7054,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -7125,7 +7124,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -7195,7 +7194,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -7265,7 +7264,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -7335,7 +7334,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -7405,7 +7404,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -7475,7 +7474,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -7545,7 +7544,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -7612,7 +7611,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -7681,7 +7680,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -7750,7 +7749,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -7819,7 +7818,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -7888,7 +7887,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -7949,7 +7948,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -8018,7 +8017,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -8087,7 +8086,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -8157,7 +8156,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -8227,7 +8226,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -8294,7 +8293,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -8358,7 +8357,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -8418,7 +8417,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -8481,7 +8480,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -8546,7 +8545,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -8608,7 +8607,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -8666,7 +8665,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -8724,7 +8723,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -8798,7 +8797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -8872,7 +8871,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -8946,7 +8945,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -9094,7 +9093,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -9168,7 +9167,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -9242,7 +9241,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>221</v>
       </c>
@@ -9306,7 +9305,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -9380,7 +9379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -9454,7 +9453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -9528,7 +9527,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -9602,7 +9601,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -9676,7 +9675,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -9750,7 +9749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>222</v>
       </c>
@@ -9824,7 +9823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -9898,7 +9897,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -9970,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -10044,7 +10043,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -10118,7 +10117,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -10178,7 +10177,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -10252,7 +10251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -10326,7 +10325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -10400,7 +10399,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -10472,7 +10471,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -10546,7 +10545,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -10620,7 +10619,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -10692,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -10766,7 +10765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -10840,7 +10839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -10914,7 +10913,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -10988,7 +10987,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -11062,7 +11061,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -11136,7 +11135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -11208,7 +11207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -11282,7 +11281,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -11352,7 +11351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -11426,7 +11425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -11496,7 +11495,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -11566,7 +11565,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -11640,7 +11639,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -11712,7 +11711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -11786,7 +11785,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -11860,7 +11859,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -11934,7 +11933,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -12008,7 +12007,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -12082,7 +12081,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -12156,7 +12155,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -12213,7 +12212,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -12269,7 +12268,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -12337,7 +12336,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -12399,7 +12398,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -12473,7 +12472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -12547,7 +12546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -12621,7 +12620,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -12695,7 +12694,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -12769,7 +12768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -12843,7 +12842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -12905,7 +12904,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -12964,7 +12963,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -13022,7 +13021,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>326</v>
       </c>
@@ -13080,7 +13079,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -13140,7 +13139,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -13196,7 +13195,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -13254,7 +13253,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -13312,7 +13311,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -13368,7 +13367,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -13426,7 +13425,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -13484,7 +13483,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
     </row>
-    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>367</v>
       </c>
@@ -13542,7 +13541,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -13600,7 +13599,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -13658,7 +13657,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -13714,7 +13713,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -13770,7 +13769,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -13826,7 +13825,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -13884,7 +13883,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -13942,7 +13941,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -14000,7 +13999,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -14056,7 +14055,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -14112,7 +14111,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -14224,7 +14223,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -14280,7 +14279,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -14336,7 +14335,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -14392,7 +14391,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
     </row>
-    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>495</v>
       </c>
@@ -14448,7 +14447,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -14504,7 +14503,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>498</v>
       </c>
@@ -14560,7 +14559,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>499</v>
       </c>
@@ -14614,7 +14613,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>500</v>
       </c>
@@ -14670,7 +14669,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>501</v>
       </c>
@@ -14726,7 +14725,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>502</v>
       </c>
@@ -14782,7 +14781,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>503</v>
       </c>
@@ -14838,7 +14837,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>504</v>
       </c>
@@ -14894,7 +14893,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>505</v>
       </c>
@@ -14950,7 +14949,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>508</v>
       </c>
@@ -15006,7 +15005,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>522</v>
       </c>
@@ -15060,7 +15059,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>527</v>
       </c>
@@ -15112,7 +15111,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>528</v>
       </c>
@@ -15167,7 +15166,7 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
     </row>
-    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>541</v>
       </c>
@@ -15221,7 +15220,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
     </row>
-    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>542</v>
       </c>
@@ -15285,7 +15284,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
     </row>
-    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>542</v>
       </c>
@@ -15359,7 +15358,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>542</v>
       </c>
@@ -15433,7 +15432,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>542</v>
       </c>
@@ -15507,7 +15506,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>542</v>
       </c>
@@ -15581,7 +15580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>546</v>
       </c>
@@ -15643,7 +15642,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
     </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>546</v>
       </c>
@@ -15714,7 +15713,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -15785,7 +15784,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -15856,7 +15855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>547</v>
       </c>
@@ -15910,7 +15909,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
     </row>
-    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>552</v>
       </c>
@@ -15964,7 +15963,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>553</v>
       </c>
@@ -16018,7 +16017,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>556</v>
       </c>
@@ -16072,7 +16071,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>290</v>
       </c>
@@ -16145,7 +16144,7 @@
         <v>91.666666666666657</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>290</v>
       </c>
@@ -16219,7 +16218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -16293,7 +16292,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -16367,7 +16366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -16441,7 +16440,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -16515,7 +16514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -16589,7 +16588,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -16663,7 +16662,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -16737,7 +16736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -16811,7 +16810,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>77</v>
       </c>
@@ -16888,7 +16887,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>121</v>
       </c>
@@ -16965,7 +16964,7 @@
         <v>99.18</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>122</v>
       </c>
@@ -17042,7 +17041,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>124</v>
       </c>
@@ -17119,7 +17118,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>125</v>
       </c>
@@ -17196,7 +17195,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>128</v>
       </c>
@@ -17273,7 +17272,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>172</v>
       </c>
@@ -17350,7 +17349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>208</v>
       </c>
@@ -17427,7 +17426,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>208</v>
       </c>
@@ -17504,7 +17503,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -17581,7 +17580,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -17658,7 +17657,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -17735,7 +17734,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -17812,7 +17811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -17889,7 +17888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>214</v>
       </c>
@@ -17966,7 +17965,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>214</v>
       </c>
@@ -18043,7 +18042,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -18120,7 +18119,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -18197,7 +18196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -18274,7 +18273,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -18351,7 +18350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -18428,7 +18427,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>217</v>
       </c>
@@ -18505,7 +18504,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>217</v>
       </c>
@@ -18582,7 +18581,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -18659,7 +18658,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -18736,7 +18735,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -18813,7 +18812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -18890,7 +18889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -18967,7 +18966,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>218</v>
       </c>
@@ -19044,7 +19043,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>218</v>
       </c>
@@ -19121,7 +19120,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -19198,7 +19197,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -19275,7 +19274,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -19352,7 +19351,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -19429,7 +19428,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -19506,7 +19505,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>225</v>
       </c>
@@ -19581,7 +19580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>225</v>
       </c>
@@ -19658,7 +19657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -19733,7 +19732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -19810,7 +19809,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -19887,7 +19886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -19964,7 +19963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -20570,7 +20569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>434</v>
       </c>
@@ -20645,7 +20644,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>434</v>
       </c>
@@ -20722,7 +20721,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -20799,7 +20798,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -20876,7 +20875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -20953,7 +20952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -21030,7 +21029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -21107,7 +21106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>436</v>
       </c>
@@ -21184,7 +21183,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>436</v>
       </c>
@@ -21261,7 +21260,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -21338,7 +21337,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>485</v>
       </c>
@@ -21411,7 +21410,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>485</v>
       </c>
@@ -21483,7 +21482,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -21557,7 +21556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -21631,7 +21630,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -21705,7 +21704,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -21779,7 +21778,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -21853,7 +21852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -21927,7 +21926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -22001,7 +22000,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -22075,7 +22074,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>488</v>
       </c>
@@ -22150,7 +22149,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>488</v>
       </c>
@@ -22224,7 +22223,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -22298,7 +22297,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -22372,7 +22371,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -22446,7 +22445,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -22520,7 +22519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -22594,7 +22593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -22668,7 +22667,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -22742,7 +22741,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -24209,7 +24208,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>68</v>
       </c>
@@ -24284,7 +24283,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>73</v>
       </c>
@@ -24361,7 +24360,7 @@
         <v>18.41</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>74</v>
       </c>
@@ -24438,7 +24437,7 @@
         <v>80.327868852459019</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>86</v>
       </c>
@@ -24515,7 +24514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>95</v>
       </c>
@@ -24592,7 +24591,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>143</v>
       </c>
@@ -24669,7 +24668,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>145</v>
       </c>
@@ -24746,7 +24745,7 @@
         <v>1.545454545454545</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>146</v>
       </c>
@@ -24823,7 +24822,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>148</v>
       </c>
@@ -24900,7 +24899,7 @@
         <v>1.977873977873978</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>159</v>
       </c>
@@ -24950,7 +24949,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>167</v>
       </c>
@@ -25021,7 +25020,7 @@
       <c r="X262" s="3"/>
       <c r="Y262" s="3"/>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>193</v>
       </c>
@@ -25086,7 +25085,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>199</v>
       </c>
@@ -25155,7 +25154,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>203</v>
       </c>
@@ -25232,7 +25231,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>203</v>
       </c>
@@ -25309,7 +25308,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -25386,7 +25385,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -25463,7 +25462,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>204</v>
       </c>
@@ -25528,7 +25527,7 @@
       <c r="X269" s="3"/>
       <c r="Y269" s="3"/>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>205</v>
       </c>
@@ -25593,7 +25592,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>207</v>
       </c>
@@ -25658,7 +25657,7 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>215</v>
       </c>
@@ -25735,7 +25734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>215</v>
       </c>
@@ -25812,7 +25811,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -25889,7 +25888,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -25966,7 +25965,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -26043,7 +26042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -26120,7 +26119,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -26197,7 +26196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>219</v>
       </c>
@@ -26272,7 +26271,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>219</v>
       </c>
@@ -26349,7 +26348,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -26426,7 +26425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -26503,7 +26502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -26580,7 +26579,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -26657,7 +26656,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -26734,7 +26733,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -26792,7 +26791,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>220</v>
       </c>
@@ -26867,7 +26866,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>220</v>
       </c>
@@ -26944,7 +26943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -27021,7 +27020,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -27098,7 +27097,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -27175,7 +27174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -27248,7 +27247,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -27325,7 +27324,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>230</v>
       </c>
@@ -27388,7 +27387,7 @@
       <c r="X294" s="3"/>
       <c r="Y294" s="3"/>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>231</v>
       </c>
@@ -27451,7 +27450,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>232</v>
       </c>
@@ -27514,7 +27513,7 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>245</v>
       </c>
@@ -27579,7 +27578,7 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>246</v>
       </c>
@@ -27642,7 +27641,7 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>252</v>
       </c>
@@ -27707,7 +27706,7 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>256</v>
       </c>
@@ -27770,7 +27769,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>260</v>
       </c>
@@ -27835,7 +27834,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>261</v>
       </c>
@@ -27900,7 +27899,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>262</v>
       </c>
@@ -27963,7 +27962,7 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>268</v>
       </c>
@@ -28028,7 +28027,7 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>269</v>
       </c>
@@ -28093,7 +28092,7 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>270</v>
       </c>
@@ -28158,7 +28157,7 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>271</v>
       </c>
@@ -28223,7 +28222,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>273</v>
       </c>
@@ -28288,7 +28287,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>274</v>
       </c>
@@ -28365,7 +28364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>274</v>
       </c>
@@ -28442,7 +28441,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -28519,7 +28518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -28596,7 +28595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -28673,7 +28672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>275</v>
       </c>
@@ -28750,7 +28749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>275</v>
       </c>
@@ -28827,7 +28826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -28904,7 +28903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -28981,7 +28980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>276</v>
       </c>
@@ -29046,7 +29045,7 @@
       <c r="X318" s="3"/>
       <c r="Y318" s="3"/>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>277</v>
       </c>
@@ -29111,7 +29110,7 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>278</v>
       </c>
@@ -29188,7 +29187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>278</v>
       </c>
@@ -29265,7 +29264,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>278</v>
       </c>
@@ -29342,7 +29341,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>278</v>
       </c>
@@ -29419,7 +29418,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>282</v>
       </c>
@@ -29484,7 +29483,7 @@
       <c r="X324" s="3"/>
       <c r="Y324" s="3"/>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>283</v>
       </c>
@@ -29549,7 +29548,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>285</v>
       </c>
@@ -29614,7 +29613,7 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>286</v>
       </c>
@@ -29691,7 +29690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>286</v>
       </c>
@@ -29768,7 +29767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>286</v>
       </c>
@@ -29845,7 +29844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>286</v>
       </c>
@@ -29922,7 +29921,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>286</v>
       </c>
@@ -29999,7 +29998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>292</v>
       </c>
@@ -30076,7 +30075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>292</v>
       </c>
@@ -30153,7 +30152,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -30230,7 +30229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -30307,7 +30306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>294</v>
       </c>
@@ -30384,7 +30383,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>294</v>
       </c>
@@ -30461,7 +30460,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -30538,7 +30537,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -30615,7 +30614,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>302</v>
       </c>
@@ -30692,7 +30691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>302</v>
       </c>
@@ -30769,7 +30768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>302</v>
       </c>
@@ -30846,7 +30845,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>302</v>
       </c>
@@ -30923,7 +30922,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>302</v>
       </c>
@@ -31000,7 +30999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>303</v>
       </c>
@@ -31075,7 +31074,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>303</v>
       </c>
@@ -31152,7 +31151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -31229,7 +31228,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -31306,7 +31305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>304</v>
       </c>
@@ -31371,7 +31370,7 @@
       <c r="X349" s="3"/>
       <c r="Y349" s="3"/>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>323</v>
       </c>
@@ -31436,7 +31435,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>324</v>
       </c>
@@ -31501,7 +31500,7 @@
       <c r="X351" s="3"/>
       <c r="Y351" s="3"/>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>325</v>
       </c>
@@ -31566,7 +31565,7 @@
       <c r="X352" s="3"/>
       <c r="Y352" s="3"/>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>327</v>
       </c>
@@ -31631,7 +31630,7 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>332</v>
       </c>
@@ -31696,7 +31695,7 @@
       <c r="X354" s="3"/>
       <c r="Y354" s="3"/>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>337</v>
       </c>
@@ -31761,7 +31760,7 @@
       <c r="X355" s="3"/>
       <c r="Y355" s="3"/>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>338</v>
       </c>
@@ -31826,7 +31825,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>341</v>
       </c>
@@ -31891,7 +31890,7 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>344</v>
       </c>
@@ -31956,7 +31955,7 @@
       <c r="X358" s="3"/>
       <c r="Y358" s="3"/>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>356</v>
       </c>
@@ -32021,7 +32020,7 @@
       <c r="X359" s="3"/>
       <c r="Y359" s="3"/>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>357</v>
       </c>
@@ -32082,7 +32081,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>358</v>
       </c>
@@ -32147,7 +32146,7 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>359</v>
       </c>
@@ -32208,7 +32207,7 @@
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -32285,7 +32284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>362</v>
       </c>
@@ -32362,7 +32361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -32439,7 +32438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>363</v>
       </c>
@@ -32502,7 +32501,7 @@
       <c r="X366" s="3"/>
       <c r="Y366" s="3"/>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>364</v>
       </c>
@@ -32567,7 +32566,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>369</v>
       </c>
@@ -32644,7 +32643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>369</v>
       </c>
@@ -32721,7 +32720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -32798,7 +32797,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>371</v>
       </c>
@@ -32863,7 +32862,7 @@
       <c r="X371" s="3"/>
       <c r="Y371" s="3"/>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>375</v>
       </c>
@@ -32940,7 +32939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -33017,7 +33016,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -33094,7 +33093,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>376</v>
       </c>
@@ -33159,7 +33158,7 @@
       <c r="X375" s="3"/>
       <c r="Y375" s="3"/>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>379</v>
       </c>
@@ -33224,7 +33223,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>381</v>
       </c>
@@ -33289,7 +33288,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>382</v>
       </c>
@@ -33354,7 +33353,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>383</v>
       </c>
@@ -33419,7 +33418,7 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>384</v>
       </c>
@@ -33484,7 +33483,7 @@
       <c r="X380" s="3"/>
       <c r="Y380" s="3"/>
     </row>
-    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>385</v>
       </c>
@@ -33549,7 +33548,7 @@
       <c r="X381" s="3"/>
       <c r="Y381" s="3"/>
     </row>
-    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>386</v>
       </c>
@@ -33626,7 +33625,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>386</v>
       </c>
@@ -33703,7 +33702,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -33780,7 +33779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -33857,7 +33856,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>389</v>
       </c>
@@ -33930,7 +33929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -34004,7 +34003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -34078,7 +34077,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -34152,7 +34151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -34226,7 +34225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -34300,7 +34299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -34374,7 +34373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -34448,7 +34447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -34522,7 +34521,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -34596,7 +34595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -34670,7 +34669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -34744,7 +34743,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -34818,7 +34817,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -34883,7 +34882,7 @@
       <c r="X399" s="3"/>
       <c r="Y399" s="3"/>
     </row>
-    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -34948,7 +34947,7 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -35013,7 +35012,7 @@
       <c r="X401" s="3"/>
       <c r="Y401" s="3"/>
     </row>
-    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -35078,7 +35077,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -35143,7 +35142,7 @@
       <c r="X403" s="3"/>
       <c r="Y403" s="3"/>
     </row>
-    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -35208,7 +35207,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>408</v>
       </c>
@@ -35285,7 +35284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -35362,7 +35361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -35439,7 +35438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -35516,7 +35515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>422</v>
       </c>
@@ -35581,7 +35580,7 @@
       <c r="X409" s="3"/>
       <c r="Y409" s="3"/>
     </row>
-    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>426</v>
       </c>
@@ -35640,7 +35639,7 @@
       <c r="X410" s="3"/>
       <c r="Y410" s="3"/>
     </row>
-    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>427</v>
       </c>
@@ -35717,7 +35716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>427</v>
       </c>
@@ -35794,7 +35793,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -35871,7 +35870,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -35948,7 +35947,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -36025,7 +36024,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -36098,7 +36097,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -36175,7 +36174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>428</v>
       </c>
@@ -36252,7 +36251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>428</v>
       </c>
@@ -36329,7 +36328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -36406,7 +36405,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -36481,7 +36480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -36558,7 +36557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -36631,7 +36630,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -36706,7 +36705,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -36760,7 +36759,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>429</v>
       </c>
@@ -36837,7 +36836,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -36914,7 +36913,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -36991,7 +36990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -37068,7 +37067,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -37145,7 +37144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -37222,7 +37221,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -37299,7 +37298,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>430</v>
       </c>
@@ -37376,7 +37375,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>430</v>
       </c>
@@ -37453,7 +37452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -37530,7 +37529,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -37607,7 +37606,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -37684,7 +37683,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>433</v>
       </c>
@@ -37761,7 +37760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>433</v>
       </c>
@@ -37838,7 +37837,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -37915,7 +37914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -37992,7 +37991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -38065,7 +38064,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -38136,7 +38135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -38211,7 +38210,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -38269,7 +38268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>435</v>
       </c>
@@ -38344,7 +38343,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>435</v>
       </c>
@@ -38421,7 +38420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -38498,7 +38497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -38575,7 +38574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -38652,7 +38651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -38729,7 +38728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -38806,7 +38805,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>439</v>
       </c>
@@ -38883,7 +38882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>439</v>
       </c>
@@ -38960,7 +38959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -39037,7 +39036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>440</v>
       </c>
@@ -39114,7 +39113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>440</v>
       </c>
@@ -39191,7 +39190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -39268,7 +39267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>444</v>
       </c>
@@ -39327,7 +39326,7 @@
       <c r="X459" s="3"/>
       <c r="Y459" s="3"/>
     </row>
-    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>445</v>
       </c>
@@ -39388,7 +39387,7 @@
       <c r="X460" s="3"/>
       <c r="Y460" s="3"/>
     </row>
-    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>447</v>
       </c>
@@ -39449,7 +39448,7 @@
       <c r="X461" s="3"/>
       <c r="Y461" s="3"/>
     </row>
-    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>448</v>
       </c>
@@ -39510,7 +39509,7 @@
       <c r="X462" s="3"/>
       <c r="Y462" s="3"/>
     </row>
-    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>451</v>
       </c>
@@ -39571,7 +39570,7 @@
       <c r="X463" s="3"/>
       <c r="Y463" s="3"/>
     </row>
-    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>452</v>
       </c>
@@ -39628,7 +39627,7 @@
       <c r="X464" s="3"/>
       <c r="Y464" s="3"/>
     </row>
-    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>466</v>
       </c>
@@ -39689,7 +39688,7 @@
       <c r="X465" s="3"/>
       <c r="Y465" s="3"/>
     </row>
-    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>467</v>
       </c>
@@ -39750,7 +39749,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
     </row>
-    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>468</v>
       </c>
@@ -39811,7 +39810,7 @@
       <c r="X467" s="3"/>
       <c r="Y467" s="3"/>
     </row>
-    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>473</v>
       </c>
@@ -39888,7 +39887,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -39965,7 +39964,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>473</v>
       </c>
@@ -40042,7 +40041,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>473</v>
       </c>
@@ -40119,7 +40118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>474</v>
       </c>
@@ -40192,7 +40191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>474</v>
       </c>
@@ -40266,7 +40265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -40340,7 +40339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -40414,7 +40413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -40488,7 +40487,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -40562,7 +40561,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -40636,7 +40635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -40710,7 +40709,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -40784,7 +40783,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -40858,7 +40857,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -40932,7 +40931,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -41006,7 +41005,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -41080,7 +41079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>475</v>
       </c>
@@ -41141,7 +41140,7 @@
       <c r="X485" s="3"/>
       <c r="Y485" s="3"/>
     </row>
-    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>476</v>
       </c>
@@ -41218,7 +41217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>476</v>
       </c>
@@ -41295,7 +41294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -41372,7 +41371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -41449,7 +41448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>477</v>
       </c>
@@ -41520,7 +41519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>477</v>
       </c>
@@ -41594,7 +41593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -41668,7 +41667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -41742,7 +41741,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -41816,7 +41815,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -41890,7 +41889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -41964,7 +41963,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -42038,7 +42037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -42112,7 +42111,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -42186,7 +42185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -42260,7 +42259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -42334,7 +42333,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -42408,7 +42407,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>478</v>
       </c>
@@ -42481,7 +42480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>478</v>
       </c>
@@ -42555,7 +42554,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -42629,7 +42628,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -42703,7 +42702,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -42777,7 +42776,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -42851,7 +42850,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -42925,7 +42924,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -42999,7 +42998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -43073,7 +43072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -43147,7 +43146,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -43221,7 +43220,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -43295,7 +43294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -43369,7 +43368,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>479</v>
       </c>
@@ -43442,7 +43441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>479</v>
       </c>
@@ -43519,7 +43518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -43596,7 +43595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -43673,7 +43672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -43750,7 +43749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -43827,7 +43826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -43904,7 +43903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -43981,7 +43980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -44058,7 +44057,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -44135,7 +44134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -44212,7 +44211,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -44289,7 +44288,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -44366,7 +44365,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>480</v>
       </c>
@@ -44439,7 +44438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>480</v>
       </c>
@@ -44516,7 +44515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -44593,7 +44592,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -44670,7 +44669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -44747,7 +44746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -44824,7 +44823,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -44901,7 +44900,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -44978,7 +44977,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -45055,7 +45054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -45132,7 +45131,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -45209,7 +45208,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -45286,7 +45285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -45363,7 +45362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>481</v>
       </c>
@@ -45424,7 +45423,7 @@
       <c r="X542" s="3"/>
       <c r="Y542" s="3"/>
     </row>
-    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>481</v>
       </c>
@@ -45494,7 +45493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>486</v>
       </c>
@@ -45553,7 +45552,7 @@
       <c r="X544" s="3"/>
       <c r="Y544" s="3"/>
     </row>
-    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>506</v>
       </c>
@@ -45612,7 +45611,7 @@
       <c r="X545" s="3"/>
       <c r="Y545" s="3"/>
     </row>
-    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>507</v>
       </c>
@@ -45671,7 +45670,7 @@
       <c r="X546" s="3"/>
       <c r="Y546" s="3"/>
     </row>
-    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>514</v>
       </c>
@@ -45728,7 +45727,7 @@
       <c r="X547" s="3"/>
       <c r="Y547" s="3"/>
     </row>
-    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>515</v>
       </c>
@@ -45783,7 +45782,7 @@
       <c r="X548" s="3"/>
       <c r="Y548" s="3"/>
     </row>
-    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>516</v>
       </c>
@@ -45838,7 +45837,7 @@
       <c r="X549" s="3"/>
       <c r="Y549" s="3"/>
     </row>
-    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>519</v>
       </c>
@@ -45915,7 +45914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>519</v>
       </c>
@@ -45992,7 +45991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -46069,7 +46068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>523</v>
       </c>
@@ -46146,7 +46145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>523</v>
       </c>
@@ -46223,7 +46222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -46300,7 +46299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -46377,7 +46376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>524</v>
       </c>
@@ -46454,7 +46453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>524</v>
       </c>
@@ -46531,7 +46530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -46608,7 +46607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -46685,7 +46684,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -46762,7 +46761,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -46839,7 +46838,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -46916,7 +46915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>530</v>
       </c>
@@ -46971,7 +46970,7 @@
       <c r="X564" s="3"/>
       <c r="Y564" s="3"/>
     </row>
-    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>531</v>
       </c>
@@ -47026,7 +47025,7 @@
       <c r="X565" s="3"/>
       <c r="Y565" s="3"/>
     </row>
-    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>532</v>
       </c>
@@ -47095,7 +47094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>532</v>
       </c>
@@ -47172,7 +47171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -47249,7 +47248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -47326,7 +47325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -47403,7 +47402,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>533</v>
       </c>
@@ -47480,7 +47479,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>533</v>
       </c>
@@ -47557,7 +47556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -47634,7 +47633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>534</v>
       </c>
@@ -47711,7 +47710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>534</v>
       </c>
@@ -47788,7 +47787,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -47865,7 +47864,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>535</v>
       </c>
@@ -47942,7 +47941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -48019,7 +48018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -48096,7 +48095,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>536</v>
       </c>
@@ -48173,7 +48172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>536</v>
       </c>
@@ -48250,7 +48249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -48327,7 +48326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>537</v>
       </c>
@@ -48384,7 +48383,7 @@
       <c r="X583" s="3"/>
       <c r="Y583" s="3"/>
     </row>
-    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>538</v>
       </c>
@@ -48439,7 +48438,7 @@
       <c r="X584" s="3"/>
       <c r="Y584" s="3"/>
     </row>
-    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>539</v>
       </c>
@@ -48494,7 +48493,7 @@
       <c r="X585" s="3"/>
       <c r="Y585" s="3"/>
     </row>
-    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>540</v>
       </c>
@@ -48551,7 +48550,7 @@
       <c r="X586" s="3"/>
       <c r="Y586" s="3"/>
     </row>
-    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>543</v>
       </c>
@@ -48626,7 +48625,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>543</v>
       </c>
@@ -48703,7 +48702,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -48780,7 +48779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>544</v>
       </c>
@@ -48855,7 +48854,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>544</v>
       </c>
@@ -48932,7 +48931,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -49009,7 +49008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -49086,7 +49085,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -49163,7 +49162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>550</v>
       </c>
@@ -49220,7 +49219,7 @@
       <c r="X595" s="3"/>
       <c r="Y595" s="3"/>
     </row>
-    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>551</v>
       </c>
@@ -49277,7 +49276,7 @@
       <c r="X596" s="3"/>
       <c r="Y596" s="3"/>
     </row>
-    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>554</v>
       </c>
@@ -49332,7 +49331,7 @@
       <c r="X597" s="3"/>
       <c r="Y597" s="3"/>
     </row>
-    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>555</v>
       </c>
@@ -49387,7 +49386,7 @@
       <c r="X598" s="3"/>
       <c r="Y598" s="3"/>
     </row>
-    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>69</v>
       </c>
@@ -49464,7 +49463,7 @@
         <v>90.541781450871994</v>
       </c>
     </row>
-    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>111</v>
       </c>
@@ -49541,7 +49540,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>197</v>
       </c>
@@ -49618,7 +49617,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>213</v>
       </c>
@@ -49695,7 +49694,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>213</v>
       </c>
@@ -49772,7 +49771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -49849,7 +49848,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -49926,7 +49925,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -50003,7 +50002,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -50080,7 +50079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -50157,7 +50156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -50234,7 +50233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -50311,7 +50310,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>233</v>
       </c>
@@ -50386,7 +50385,7 @@
         <v>64.367816091954026</v>
       </c>
     </row>
-    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>234</v>
       </c>
@@ -50461,7 +50460,7 @@
         <v>3692.25</v>
       </c>
     </row>
-    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>238</v>
       </c>
@@ -50534,7 +50533,7 @@
         <v>94.444444444444443</v>
       </c>
     </row>
-    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>238</v>
       </c>
@@ -50611,7 +50610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -50688,7 +50687,7 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -50765,7 +50764,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -50842,7 +50841,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -50919,7 +50918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -50996,7 +50995,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -51073,7 +51072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -51225,7 +51224,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>251</v>
       </c>
@@ -51300,7 +51299,7 @@
       </c>
       <c r="Y623" s="3"/>
     </row>
-    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>254</v>
       </c>
@@ -51356,7 +51355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>263</v>
       </c>
@@ -51433,7 +51432,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>265</v>
       </c>
@@ -51510,7 +51509,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>266</v>
       </c>
@@ -51587,7 +51586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>300</v>
       </c>
@@ -51664,7 +51663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>301</v>
       </c>
@@ -51741,7 +51740,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>306</v>
       </c>
@@ -51816,7 +51815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>306</v>
       </c>
@@ -51893,7 +51892,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -51970,7 +51969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -52047,7 +52046,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -52124,7 +52123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -52201,7 +52200,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -52278,7 +52277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>347</v>
       </c>
@@ -52355,7 +52354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>348</v>
       </c>
@@ -52432,7 +52431,7 @@
         <v>99.936143039591002</v>
       </c>
     </row>
-    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>351</v>
       </c>
@@ -52507,7 +52506,7 @@
         <v>11.41868512110727</v>
       </c>
     </row>
-    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>352</v>
       </c>
@@ -52582,7 +52581,7 @@
         <v>1.0385968556480199E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>368</v>
       </c>
@@ -52655,7 +52654,7 @@
       <c r="X641" s="3"/>
       <c r="Y641" s="3"/>
     </row>
-    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>372</v>
       </c>
@@ -52728,7 +52727,7 @@
       <c r="X642" s="3"/>
       <c r="Y642" s="3"/>
     </row>
-    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>373</v>
       </c>
@@ -52805,7 +52804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>373</v>
       </c>
@@ -52882,7 +52881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -52959,7 +52958,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -53036,7 +53035,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -53113,7 +53112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -53190,7 +53189,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -53267,7 +53266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>390</v>
       </c>
@@ -53344,7 +53343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>390</v>
       </c>
@@ -53421,7 +53420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -53498,7 +53497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -53575,7 +53574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -53652,7 +53651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -53729,7 +53728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -53806,7 +53805,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -53883,7 +53882,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -53960,7 +53959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -54037,7 +54036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -54114,7 +54113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -54191,7 +54190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -54268,7 +54267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>394</v>
       </c>
@@ -54345,7 +54344,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>395</v>
       </c>
@@ -54420,7 +54419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>409</v>
       </c>
@@ -54491,7 +54490,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>409</v>
       </c>
@@ -54568,7 +54567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -54645,7 +54644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>414</v>
       </c>
@@ -54722,7 +54721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>414</v>
       </c>
@@ -54799,7 +54798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -54876,7 +54875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -54953,7 +54952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -55030,7 +55029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -55107,7 +55106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -55184,7 +55183,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -55261,7 +55260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -55338,7 +55337,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -55415,7 +55414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>415</v>
       </c>
@@ -55492,7 +55491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>415</v>
       </c>
@@ -55569,7 +55568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -55646,7 +55645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -55723,7 +55722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -55800,7 +55799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -55877,7 +55876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -55954,7 +55953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -56031,7 +56030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -56108,7 +56107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -56185,7 +56184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -56262,7 +56261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -56339,7 +56338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -56416,7 +56415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -56493,7 +56492,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -56570,7 +56569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>416</v>
       </c>
@@ -56647,7 +56646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>416</v>
       </c>
@@ -56724,7 +56723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -56801,7 +56800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -56878,7 +56877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -56955,7 +56954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -57032,7 +57031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -57109,7 +57108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>417</v>
       </c>
@@ -57186,7 +57185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>417</v>
       </c>
@@ -57263,7 +57262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -57340,7 +57339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -57417,7 +57416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -57494,7 +57493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -57571,7 +57570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -57648,7 +57647,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>418</v>
       </c>
@@ -57725,7 +57724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>418</v>
       </c>
@@ -57802,7 +57801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -57879,7 +57878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -57956,7 +57955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -58031,7 +58030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -58108,7 +58107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -58185,7 +58184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -58262,7 +58261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -58339,7 +58338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -58416,7 +58415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>420</v>
       </c>
@@ -58493,7 +58492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>420</v>
       </c>
@@ -58570,7 +58569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -58647,7 +58646,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -58724,7 +58723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -58801,7 +58800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -58878,7 +58877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -58955,7 +58954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>431</v>
       </c>
@@ -59028,7 +59027,7 @@
       <c r="X724" s="3"/>
       <c r="Y724" s="3"/>
     </row>
-    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>432</v>
       </c>
@@ -59105,7 +59104,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>432</v>
       </c>
@@ -59182,7 +59181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -59259,7 +59258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -59336,7 +59335,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -59413,7 +59412,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -59490,7 +59489,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -59567,7 +59566,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -59644,7 +59643,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -59721,7 +59720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -59798,7 +59797,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>453</v>
       </c>
@@ -59867,7 +59866,7 @@
       <c r="X735" s="3"/>
       <c r="Y735" s="3"/>
     </row>
-    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>455</v>
       </c>
@@ -59932,7 +59931,7 @@
       <c r="X736" s="3"/>
       <c r="Y736" s="3"/>
     </row>
-    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>456</v>
       </c>
@@ -60003,7 +60002,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>456</v>
       </c>
@@ -60080,7 +60079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -60157,7 +60156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -60234,7 +60233,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>457</v>
       </c>
@@ -60305,7 +60304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>457</v>
       </c>
@@ -60382,7 +60381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -60459,7 +60458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -60536,7 +60535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>469</v>
       </c>
@@ -60611,7 +60610,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>469</v>
       </c>
@@ -60688,7 +60687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -60765,7 +60764,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -60842,7 +60841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -60919,7 +60918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -60996,7 +60995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -61073,7 +61072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -61150,7 +61149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -61227,7 +61226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -61304,7 +61303,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -61381,7 +61380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>470</v>
       </c>
@@ -61458,7 +61457,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>470</v>
       </c>
@@ -61533,7 +61532,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -61610,7 +61609,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -61687,7 +61686,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -61764,7 +61763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -61841,7 +61840,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>471</v>
       </c>
@@ -61918,7 +61917,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>471</v>
       </c>
@@ -61995,7 +61994,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -62072,7 +62071,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -62149,7 +62148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -62226,7 +62225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -62303,7 +62302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -62380,7 +62379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -62457,7 +62456,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>484</v>
       </c>
@@ -62524,7 +62523,7 @@
       <c r="X770" s="3"/>
       <c r="Y770" s="3"/>
     </row>
-    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>510</v>
       </c>
@@ -62599,7 +62598,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>510</v>
       </c>
@@ -62670,7 +62669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>511</v>
       </c>
@@ -62745,7 +62744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>511</v>
       </c>
@@ -62822,7 +62821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -62899,7 +62898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -62976,7 +62975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -63053,7 +63052,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -63130,7 +63129,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -63207,7 +63206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -63284,7 +63283,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>513</v>
       </c>
@@ -63345,7 +63344,7 @@
       <c r="X781" s="3"/>
       <c r="Y781" s="3"/>
     </row>
-    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>518</v>
       </c>
@@ -63399,7 +63398,7 @@
       </c>
       <c r="R782" s="3"/>
     </row>
-    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>526</v>
       </c>
@@ -63456,7 +63455,7 @@
       <c r="X783" s="3"/>
       <c r="Y783" s="3"/>
     </row>
-    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>529</v>
       </c>
@@ -63531,7 +63530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A785">
         <v>529</v>
       </c>
@@ -63608,7 +63607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -63687,13 +63686,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Gestión de Proyectos"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
@@ -63702,7 +63694,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C20A0A1-9BF9-429B-8551-A92A07A2B5F1}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA298"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -63793,7 +63784,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -63871,7 +63862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -63949,7 +63940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -64027,7 +64018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -64105,7 +64096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -64183,7 +64174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -64261,7 +64252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -64339,7 +64330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -64417,7 +64408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -64495,7 +64486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -64573,7 +64564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -64651,7 +64642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -64729,7 +64720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -64804,7 +64795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -64881,7 +64872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -64958,7 +64949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -65035,7 +65026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -65112,7 +65103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -65181,7 +65172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -65258,7 +65249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -65335,7 +65326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -65413,7 +65404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -65491,7 +65482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -65566,7 +65557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -65638,7 +65629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -65706,7 +65697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -65777,7 +65768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -65850,7 +65841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -65920,7 +65911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -65986,7 +65977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -66052,7 +66043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -66134,7 +66125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>221</v>
       </c>
@@ -66206,7 +66197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>222</v>
       </c>
@@ -66288,7 +66279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>223</v>
       </c>
@@ -66368,7 +66359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>224</v>
       </c>
@@ -66436,7 +66427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>226</v>
       </c>
@@ -66516,7 +66507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>227</v>
       </c>
@@ -66596,7 +66587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>228</v>
       </c>
@@ -66676,7 +66667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>235</v>
       </c>
@@ -66741,7 +66732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>236</v>
       </c>
@@ -66805,7 +66796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>244</v>
       </c>
@@ -66881,7 +66872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>255</v>
       </c>
@@ -66951,7 +66942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>272</v>
       </c>
@@ -67021,7 +67012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>288</v>
       </c>
@@ -67088,7 +67079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>318</v>
       </c>
@@ -67154,7 +67145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>326</v>
       </c>
@@ -67220,7 +67211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>334</v>
       </c>
@@ -67288,7 +67279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>336</v>
       </c>
@@ -67352,7 +67343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>339</v>
       </c>
@@ -67418,7 +67409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>346</v>
       </c>
@@ -67484,7 +67475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>355</v>
       </c>
@@ -67548,7 +67539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>361</v>
       </c>
@@ -67614,7 +67605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>366</v>
       </c>
@@ -67680,7 +67671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>367</v>
       </c>
@@ -67746,7 +67737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>377</v>
       </c>
@@ -67812,7 +67803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>392</v>
       </c>
@@ -67878,7 +67869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>393</v>
       </c>
@@ -67942,7 +67933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>402</v>
       </c>
@@ -68006,7 +67997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>413</v>
       </c>
@@ -68070,7 +68061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>423</v>
       </c>
@@ -68136,7 +68127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>424</v>
       </c>
@@ -68202,7 +68193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>437</v>
       </c>
@@ -68268,7 +68259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>460</v>
       </c>
@@ -70055,7 +70046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>290</v>
       </c>
@@ -70136,7 +70127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>77</v>
       </c>
@@ -70221,7 +70212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>121</v>
       </c>
@@ -70306,7 +70297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>122</v>
       </c>
@@ -70391,7 +70382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>124</v>
       </c>
@@ -70476,7 +70467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>125</v>
       </c>
@@ -70561,7 +70552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>128</v>
       </c>
@@ -70646,7 +70637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>172</v>
       </c>
@@ -70731,7 +70722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>208</v>
       </c>
@@ -70816,7 +70807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>214</v>
       </c>
@@ -70901,7 +70892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>217</v>
       </c>
@@ -70986,7 +70977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>218</v>
       </c>
@@ -71071,7 +71062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>225</v>
       </c>
@@ -71154,7 +71145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>239</v>
       </c>
@@ -71239,7 +71230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>241</v>
       </c>
@@ -71316,7 +71307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>434</v>
       </c>
@@ -71399,7 +71390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>436</v>
       </c>
@@ -71717,7 +71708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>68</v>
       </c>
@@ -71800,7 +71791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>73</v>
       </c>
@@ -71885,7 +71876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>74</v>
       </c>
@@ -71970,7 +71961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>86</v>
       </c>
@@ -72055,7 +72046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>95</v>
       </c>
@@ -72140,7 +72131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>143</v>
       </c>
@@ -72225,7 +72216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>145</v>
       </c>
@@ -72310,7 +72301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>146</v>
       </c>
@@ -72395,7 +72386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>148</v>
       </c>
@@ -72480,7 +72471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>159</v>
       </c>
@@ -72538,7 +72529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>167</v>
       </c>
@@ -72617,7 +72608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>193</v>
       </c>
@@ -72690,7 +72681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>199</v>
       </c>
@@ -72767,7 +72758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>203</v>
       </c>
@@ -72852,7 +72843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>204</v>
       </c>
@@ -72925,7 +72916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>205</v>
       </c>
@@ -72998,7 +72989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>207</v>
       </c>
@@ -73071,7 +73062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>215</v>
       </c>
@@ -73156,7 +73147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>219</v>
       </c>
@@ -73239,7 +73230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>220</v>
       </c>
@@ -73322,7 +73313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>230</v>
       </c>
@@ -73393,7 +73384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>231</v>
       </c>
@@ -73464,7 +73455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>232</v>
       </c>
@@ -73535,7 +73526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>245</v>
       </c>
@@ -73608,7 +73599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>246</v>
       </c>
@@ -73679,7 +73670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>252</v>
       </c>
@@ -73752,7 +73743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>256</v>
       </c>
@@ -73823,7 +73814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>260</v>
       </c>
@@ -73896,7 +73887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>261</v>
       </c>
@@ -73969,7 +73960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>262</v>
       </c>
@@ -74040,7 +74031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>268</v>
       </c>
@@ -74113,7 +74104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>269</v>
       </c>
@@ -74186,7 +74177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>270</v>
       </c>
@@ -74259,7 +74250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>271</v>
       </c>
@@ -74332,7 +74323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>273</v>
       </c>
@@ -74405,7 +74396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>274</v>
       </c>
@@ -74490,7 +74481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>275</v>
       </c>
@@ -74575,7 +74566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>276</v>
       </c>
@@ -74648,7 +74639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>277</v>
       </c>
@@ -74721,7 +74712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>278</v>
       </c>
@@ -74806,7 +74797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>282</v>
       </c>
@@ -74879,7 +74870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>283</v>
       </c>
@@ -74952,7 +74943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>285</v>
       </c>
@@ -75025,7 +75016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>286</v>
       </c>
@@ -75110,7 +75101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>292</v>
       </c>
@@ -75195,7 +75186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>294</v>
       </c>
@@ -75280,7 +75271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>302</v>
       </c>
@@ -75365,7 +75356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>303</v>
       </c>
@@ -75448,7 +75439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>304</v>
       </c>
@@ -75521,7 +75512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>323</v>
       </c>
@@ -75594,7 +75585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>324</v>
       </c>
@@ -75667,7 +75658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>325</v>
       </c>
@@ -75740,7 +75731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>327</v>
       </c>
@@ -75813,7 +75804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>332</v>
       </c>
@@ -75886,7 +75877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>337</v>
       </c>
@@ -75959,7 +75950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>338</v>
       </c>
@@ -76032,7 +76023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>341</v>
       </c>
@@ -76105,7 +76096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>344</v>
       </c>
@@ -76178,7 +76169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>356</v>
       </c>
@@ -76251,7 +76242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>357</v>
       </c>
@@ -76320,7 +76311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>358</v>
       </c>
@@ -76393,7 +76384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>359</v>
       </c>
@@ -76462,7 +76453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>362</v>
       </c>
@@ -76547,7 +76538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>363</v>
       </c>
@@ -76618,7 +76609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>364</v>
       </c>
@@ -76691,7 +76682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>369</v>
       </c>
@@ -76776,7 +76767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>371</v>
       </c>
@@ -76849,7 +76840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>375</v>
       </c>
@@ -76934,7 +76925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>376</v>
       </c>
@@ -77007,7 +76998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>379</v>
       </c>
@@ -77080,7 +77071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>381</v>
       </c>
@@ -77153,7 +77144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>382</v>
       </c>
@@ -77226,7 +77217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>383</v>
       </c>
@@ -77299,7 +77290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>384</v>
       </c>
@@ -77372,7 +77363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>385</v>
       </c>
@@ -77445,7 +77436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>386</v>
       </c>
@@ -77530,7 +77521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>389</v>
       </c>
@@ -77611,7 +77602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>397</v>
       </c>
@@ -77684,7 +77675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>398</v>
       </c>
@@ -77757,7 +77748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>399</v>
       </c>
@@ -77830,7 +77821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>400</v>
       </c>
@@ -77903,7 +77894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>401</v>
       </c>
@@ -77976,7 +77967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>403</v>
       </c>
@@ -78049,7 +78040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>408</v>
       </c>
@@ -78134,7 +78125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>422</v>
       </c>
@@ -78207,7 +78198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>426</v>
       </c>
@@ -78274,7 +78265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>427</v>
       </c>
@@ -78359,7 +78350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>428</v>
       </c>
@@ -78444,7 +78435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>429</v>
       </c>
@@ -78529,7 +78520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>430</v>
       </c>
@@ -78614,7 +78605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>433</v>
       </c>
@@ -78699,7 +78690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>435</v>
       </c>
@@ -78782,7 +78773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>439</v>
       </c>
@@ -78867,7 +78858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>440</v>
       </c>
@@ -78952,7 +78943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>444</v>
       </c>
@@ -79019,7 +79010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>445</v>
       </c>
@@ -79088,7 +79079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>447</v>
       </c>
@@ -79157,7 +79148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>448</v>
       </c>
@@ -79226,7 +79217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>451</v>
       </c>
@@ -79295,7 +79286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>452</v>
       </c>
@@ -79360,7 +79351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>466</v>
       </c>
@@ -79429,7 +79420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>467</v>
       </c>
@@ -79498,7 +79489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>468</v>
       </c>
@@ -79567,7 +79558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>473</v>
       </c>
@@ -79652,7 +79643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>474</v>
       </c>
@@ -79802,7 +79793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>476</v>
       </c>
@@ -82146,7 +82137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>69</v>
       </c>
@@ -82231,7 +82222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>111</v>
       </c>
@@ -82316,7 +82307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>197</v>
       </c>
@@ -82401,7 +82392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>213</v>
       </c>
@@ -82486,7 +82477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>233</v>
       </c>
@@ -82569,7 +82560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>234</v>
       </c>
@@ -82652,7 +82643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>238</v>
       </c>
@@ -82733,7 +82724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>240</v>
       </c>
@@ -82816,7 +82807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>251</v>
       </c>
@@ -82899,7 +82890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>254</v>
       </c>
@@ -82963,7 +82954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>263</v>
       </c>
@@ -83048,7 +83039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>265</v>
       </c>
@@ -83133,7 +83124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>266</v>
       </c>
@@ -83218,7 +83209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>300</v>
       </c>
@@ -83303,7 +83294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>301</v>
       </c>
@@ -83388,7 +83379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>306</v>
       </c>
@@ -83471,7 +83462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>347</v>
       </c>
@@ -83556,7 +83547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>348</v>
       </c>
@@ -83641,7 +83632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>351</v>
       </c>
@@ -83724,7 +83715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>352</v>
       </c>
@@ -83807,7 +83798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>368</v>
       </c>
@@ -83888,7 +83879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>372</v>
       </c>
@@ -83969,7 +83960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>373</v>
       </c>
@@ -84054,7 +84045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>390</v>
       </c>
@@ -84139,7 +84130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>394</v>
       </c>
@@ -84224,7 +84215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>395</v>
       </c>
@@ -84307,7 +84298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>409</v>
       </c>
@@ -84386,7 +84377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>414</v>
       </c>
@@ -84471,7 +84462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>415</v>
       </c>
@@ -84556,7 +84547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>416</v>
       </c>
@@ -84641,7 +84632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>417</v>
       </c>
@@ -84726,7 +84717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>418</v>
       </c>
@@ -84811,7 +84802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>420</v>
       </c>
@@ -84896,7 +84887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>431</v>
       </c>
@@ -84977,7 +84968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>432</v>
       </c>
@@ -85062,7 +85053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>453</v>
       </c>
@@ -85139,7 +85130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>455</v>
       </c>
@@ -85212,7 +85203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>456</v>
       </c>
@@ -85291,7 +85282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>457</v>
       </c>
@@ -85370,7 +85361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>469</v>
       </c>
@@ -85453,7 +85444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>470</v>
       </c>
@@ -85538,7 +85529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>471</v>
       </c>
@@ -85623,7 +85614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>484</v>
       </c>
@@ -86145,13 +86136,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:AA298" xr:uid="{2C20A0A1-9BF9-429B-8551-A92A07A2B5F1}">
-    <filterColumn colId="25">
-      <filters>
-        <filter val="#N/D"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D522549C-79D0-4771-970F-C66CD7E8BE93}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3358D84-D433-4F6B-83FC-DDE9F520F32A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -6623,7 +6623,9 @@
   <dimension ref="A1:Y786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="25" width="9.109375" customWidth="1"/>
+    <col min="1" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="25" width="9.109375" customWidth="1"/>
     <col min="26" max="254" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
